--- a/results/job_matches_2026-05-21.xlsx
+++ b/results/job_matches_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management, Business Analytics, Associate - New York</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, GCP, BigQuery</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4ad76c8612e4a09</t>
+          <t>https://www.indeed.com/viewjob?jk=cb7a229032adf836</t>
         </is>
       </c>
     </row>
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,102 +566,102 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e0bd72df7d3118</t>
+          <t>https://www.indeed.com/viewjob?jk=994cd29faebe482b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Associate - AI Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, IAM, Databricks, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cc5523e609d6490</t>
+          <t>https://www.indeed.com/viewjob?jk=62e0bd72df7d3118</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Data Engineer I</t>
+          <t>Senior Associate - AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Honda Motor</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Marysville, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, EMR, Redshift, S3, IAM, Databricks, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17713297f88b607</t>
+          <t>https://www.indeed.com/viewjob?jk=9cc5523e609d6490</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS, python</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc48402a0ee4138</t>
+          <t>https://www.indeed.com/viewjob?jk=e9b4743d0857d2b3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - AWS, python</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef768a7022d9b02</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc48402a0ee4138</t>
         </is>
       </c>
     </row>
@@ -736,29 +736,29 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d2f3a6f6a24726d</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef768a7022d9b02</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr AI/ML Engineer - Remote Nationwide or Hybrid in MN/DC</t>
+          <t>Senior Data/AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5428c5fe3301bb2</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7b2e289fa4a81b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data/AI Engineer</t>
+          <t>Sr AI/ML Engineer - Remote Nationwide or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7b2e289fa4a81b</t>
+          <t>https://www.indeed.com/viewjob?jk=a5428c5fe3301bb2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - AI/ML</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f0117f05675ce7</t>
+          <t>https://www.indeed.com/viewjob?jk=97dc64be66ad66cd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Machine Learning Engineer - AI/ML</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,19 +881,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01411b771339e7f8</t>
+          <t>https://www.indeed.com/viewjob?jk=37f0117f05675ce7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0b54505ba83c83</t>
+          <t>https://www.indeed.com/viewjob?jk=f74dc1ef788e458e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Snowflake, Dimensional Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788be6fbb8bd5c28</t>
+          <t>https://www.indeed.com/viewjob?jk=a037ad0869b5968b</t>
         </is>
       </c>
     </row>
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d2969a0188cb3d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0b54505ba83c83</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr. Data Engineer -ITDDP (Contractual)</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7979c28cb86f5690</t>
+          <t>https://www.indeed.com/viewjob?jk=788be6fbb8bd5c28</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Data Engineering (GCP &amp; AI) (contract)</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864bf732311fb751</t>
+          <t>https://www.indeed.com/viewjob?jk=01d2969a0188cb3d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, ECS, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc070bfe12f04a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=d36804ce64799b9c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>System Engineer- Platform/API Gateway</t>
+          <t>Data Engineer/Sr. Data Engineer -ITDDP (Contractual)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>O'Reilly Auto Parts</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f3ba65fc8111094</t>
+          <t>https://www.indeed.com/viewjob?jk=7979c28cb86f5690</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer – Data Engineering (GCP &amp; AI) (contract)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32851dd10ee0e5da</t>
+          <t>https://www.indeed.com/viewjob?jk=864bf732311fb751</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=708d5186ef13d22a</t>
+          <t>https://www.indeed.com/viewjob?jk=cc070bfe12f04a4e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>System Engineer- Platform/API Gateway</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>O'Reilly Auto Parts</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
+          <t>API Gateway, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab11bf9d3a0cb66</t>
+          <t>https://www.indeed.com/viewjob?jk=9f3ba65fc8111094</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,137 +1266,137 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4179f9ef43c111</t>
+          <t>https://www.indeed.com/viewjob?jk=32851dd10ee0e5da</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GCP Data Eng</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, ETL, Jenkins, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa07fecdad59559</t>
+          <t>https://www.indeed.com/viewjob?jk=708d5186ef13d22a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Data Services Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Driscoll's</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Watsonville, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, RDS, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8cfdb0127f0b1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab11bf9d3a0cb66</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Spark, Scala, DynamoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67cc5c5d1b62b505</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4179f9ef43c111</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Database Administrator (DBA)/ETL Engineer</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, Snowflake, Time Travel, Oracle, SQL Server, DynamoDB</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98b32025713e041a</t>
+          <t>https://www.indeed.com/viewjob?jk=20e07fcacb80c198</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Services Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Driscoll's</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Watsonville, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913ce0d28b943134</t>
+          <t>https://www.indeed.com/viewjob?jk=c8cfdb0127f0b1e9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Computer Vision</t>
+          <t>GCP Data Eng</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, ETL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808de345c459337e</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa07fecdad59559</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior AWS Solution Architect</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Random Bit</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Jenkins, Docker</t>
+          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Spark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f8e7a290e072e8</t>
+          <t>https://www.indeed.com/viewjob?jk=67cc5c5d1b62b505</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AWS Solution Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Random Bit</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e671763f13a7a97</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f8e7a290e072e8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - MTS</t>
+          <t>Senior Machine Learning Engineer, Computer Vision</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa29de43e62d8b14</t>
+          <t>https://www.indeed.com/viewjob?jk=808de345c459337e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior DB engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560a0ac785ae0307</t>
+          <t>https://www.indeed.com/viewjob?jk=6e671763f13a7a97</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Software Engineer (Backend) - MTS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,69 +1641,69 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62f3b2380e0b366</t>
+          <t>https://www.indeed.com/viewjob?jk=aa29de43e62d8b14</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2139ccd23148ef97</t>
+          <t>https://www.indeed.com/viewjob?jk=d62f3b2380e0b366</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Data Engineer-Architecture</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Raiz Federal Credit Union</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979fd479106b8582</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2c98f7e4333c03</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud AWS Support Reliability Engineer (SRE)</t>
+          <t>DevOps Engineer - ML &amp; Data Infrastructure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of New York</t>
+          <t>High 5 Games</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Scala, Oracle</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=397e7786631910d4</t>
+          <t>https://www.indeed.com/viewjob?jk=5b06e51cccf7a7ba</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Newity LLC</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, BigQuery</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f118becd7bebc8f7</t>
+          <t>https://www.indeed.com/viewjob?jk=2139ccd23148ef97</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Architect - Data Platform &amp; AI/ML</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2413d561f12c179</t>
+          <t>https://www.indeed.com/viewjob?jk=979fd479106b8582</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Temporary)</t>
+          <t>Cloud AWS Support Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Brooks Running</t>
+          <t>Federal Reserve Bank of New York</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala, MLOps</t>
+          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e77238a1b70a49</t>
+          <t>https://www.indeed.com/viewjob?jk=397e7786631910d4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a04d34ff6293d7a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5de3c33ef7437dd2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Air Today USA</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,19 +1931,19 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c73ef9f43ca54c71</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d258aa3e235071</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mid-level DevOps Engineer</t>
+          <t>Senior Software Architect - Data Platform &amp; AI/ML</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ella Wholesales Coffee</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02374e2f05fa51aa</t>
+          <t>https://www.indeed.com/viewjob?jk=d2413d561f12c179</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Machine Learning Engineer (Temporary)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Brooks Running</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8bd188504a235ef</t>
+          <t>https://www.indeed.com/viewjob?jk=31e77238a1b70a49</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd3a2400ded0ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=a04d34ff6293d7a2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>El Toro.com</t>
+          <t>Air Today USA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3113d217a11359b</t>
+          <t>https://www.indeed.com/viewjob?jk=c73ef9f43ca54c71</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>Mid-level DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Ella Wholesales Coffee</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, MySQL, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dcc5ce5e437bc35</t>
+          <t>https://www.indeed.com/viewjob?jk=02374e2f05fa51aa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Platform Architect - AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e294cc6d33384a45</t>
+          <t>https://www.indeed.com/viewjob?jk=b8bd188504a235ef</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Build and Release Management</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe77948a6745c2be</t>
+          <t>https://www.indeed.com/viewjob?jk=acd3a2400ded0ef7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ideal Business Advisors</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Spark Streaming, Kafka, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, MySQL, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e07e4d5100d0a09</t>
+          <t>https://www.indeed.com/viewjob?jk=7dcc5ce5e437bc35</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>El Toro.com</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225bdb7f78f14470</t>
+          <t>https://www.indeed.com/viewjob?jk=c3113d217a11359b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Platform Architect - AI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d61f658ab71dc3d</t>
+          <t>https://www.indeed.com/viewjob?jk=e294cc6d33384a45</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer, Build and Release Management</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
+          <t>AWS, RDS, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a20b18aa66e51d2</t>
+          <t>https://www.indeed.com/viewjob?jk=fe77948a6745c2be</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Periscope</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd4f1b922a309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=354c512d0fde6f2b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Humbly Confident Senior Laravel Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Chiro Cat</t>
+          <t>Ideal Business Advisors</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, MySQL, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Spark, Spark Streaming, Kafka, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d426212b47f2cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=5e07e4d5100d0a09</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Clayco</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fb9d94196cc44d</t>
+          <t>https://www.indeed.com/viewjob?jk=225bdb7f78f14470</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Cloud Storage, Spark, PySpark, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d0b722ecec30e9</t>
+          <t>https://www.indeed.com/viewjob?jk=2d61f658ab71dc3d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, S3, ECS, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2682fedab4a2d801</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd5378e4194090a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>SolarWinds</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, BigQuery, Vertex AI, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Star Schema, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e56c8a333352b48</t>
+          <t>https://www.indeed.com/viewjob?jk=1c073df0d353c1af</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Distributed Systems Engineer, Energy Service Engineering</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Spark Streaming, Kafka, ELT, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b311adc4e009a8c4</t>
+          <t>https://www.indeed.com/viewjob?jk=74ab129070123bd2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - Applied AI - Senior - Financial Services - Consulting</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Vertex AI, Scala, Docker, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=264d256d1f44f81a</t>
+          <t>https://www.indeed.com/viewjob?jk=add6f4354189f849</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Business Systems &amp; Integrations Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6abc49ee6c2f3b4f</t>
+          <t>https://www.indeed.com/viewjob?jk=0a20b18aa66e51d2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Clayco</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9012b2ffe5f7c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fb9d94196cc44d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Data Engineer - Periscope</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d4f32f720c7b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd4f1b922a309e4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer - NYC / Dallas / Los Angeles</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Portfolio BI</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Cloud Storage, Spark, PySpark, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e72e9173a4b1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d0b722ecec30e9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Python Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Power BI, DataOps, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f910656c4ac5af</t>
+          <t>https://www.indeed.com/viewjob?jk=583b4c9601400970</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Humbly Confident Senior Laravel Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Chiro Cat</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, MySQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1897a63fde0954</t>
+          <t>https://www.indeed.com/viewjob?jk=3d426212b47f2cb5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17aeeb541c761336</t>
+          <t>https://www.indeed.com/viewjob?jk=971c26dff07c1bdc</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Sr. Distributed Systems Engineer, Energy Service Engineering</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Spark Streaming, Kafka, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637b19c57d2d2f1f</t>
+          <t>https://www.indeed.com/viewjob?jk=b311adc4e009a8c4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>Senior Business Systems &amp; Integrations Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c5dcb3f5dd6592</t>
+          <t>https://www.indeed.com/viewjob?jk=6abc49ee6c2f3b4f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Field Engineer</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Florence HC</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f35f177eb851ec</t>
+          <t>https://www.indeed.com/viewjob?jk=2682fedab4a2d801</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Intern</t>
+          <t>Forward Deployed Engineer - Applied AI - Senior - Financial Services - Consulting</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Vertex AI, Scala, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e62e31febbb7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=264d256d1f44f81a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Full Stack Quantitative Developer - NYC / Dallas / Los Angeles</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Portfolio BI</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SQS, SNS, Hadoop, Hive, HBase, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4594ef27276bcddb</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e72e9173a4b1e5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer II - Analytics</t>
+          <t>Python Full Stack Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15bd37695704d0b2</t>
+          <t>https://www.indeed.com/viewjob?jk=71f910656c4ac5af</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer - Consultant</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Releady</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, SQL Server, dbt, Tableau, CI/CD, Git, Bitbucket</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c8d9977ea88967</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c5dcb3f5dd6592</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, S3, GCP, BigQuery, Vertex AI, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116361549f755a48</t>
+          <t>https://www.indeed.com/viewjob?jk=5e56c8a333352b48</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer Go Outdoors</t>
+          <t>Field Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Florence HC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e38fd8d0926139</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f35f177eb851ec</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Informatics Architect</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Gritter Francona, Inc</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Fact Tables, Dimension Tables, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9c3829227dd781</t>
+          <t>https://www.indeed.com/viewjob?jk=d9012b2ffe5f7c5e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Informatics Architect</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Gritter Francona, Inc</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Fact Tables, Dimension Tables, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b067d12eb88dd1</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7fe3299d9494b8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Informatics Architect</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Gritter Francona, Inc</t>
+          <t>Harbinger Motors Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Garden Grove, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Fact Tables, Dimension Tables, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7ad78f557a45964</t>
+          <t>https://www.indeed.com/viewjob?jk=1042fb894a308b35</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Informatics Architect</t>
+          <t>Data Engineer II - Analytics</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Gritter Francona, Inc</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Fact Tables, Dimension Tables, Power BI, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acdf9d3eb5360a9e</t>
+          <t>https://www.indeed.com/viewjob?jk=15bd37695704d0b2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - Remote -W2 Only</t>
+          <t>Full Stack Intern</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Digital iTechnology</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket, Python</t>
+          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef52a4058b83ad57</t>
+          <t>https://www.indeed.com/viewjob?jk=15e62e31febbb7dd</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SRE / DevOps Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>SQS, SNS, Hadoop, Hive, HBase, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b064c172d457476</t>
+          <t>https://www.indeed.com/viewjob?jk=4594ef27276bcddb</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer</t>
+          <t>Senior AI/ML Full Stack Engineer – Generative AI</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfea9e97e390496</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd2d5932a298301</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Software Engineer Go Outdoors</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90f91c50a68c29bc</t>
+          <t>https://www.indeed.com/viewjob?jk=c6e38fd8d0926139</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Walkme</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bee16f62d775ab</t>
+          <t>https://www.indeed.com/viewjob?jk=116361549f755a48</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Walkme</t>
+          <t>Platform of Greatness</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2363b9cbfb0252a</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a0aff866de84b2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Full Stack Engineer - Remote -W2 Only</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Walkme</t>
+          <t>Digital iTechnology</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,15 +3531,190 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket, Python</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef52a4058b83ad57</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Changeis, Inc.</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Kafka, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90f91c50a68c29bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>AI Software Engineer (Vehicle Engineering)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SpaceX</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Hawthorne, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RDS, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad497f523694b96c</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Walkme</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37bee16f62d775ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Walkme</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2363b9cbfb0252a</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Walkme</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2d9f2d75fa67499b</t>
         </is>

--- a/results/job_matches_2026-05-21.xlsx
+++ b/results/job_matches_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>AWS Data Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>WinWire</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,59 +496,59 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb7a229032adf836</t>
+          <t>https://www.indeed.com/viewjob?jk=94da66580e29e534</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Data Architect</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WinWire</t>
+          <t>Ideas2IT Technologies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, RDS, Azure, GCP, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94da66580e29e534</t>
+          <t>https://www.indeed.com/viewjob?jk=65ba785f54845637</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=994cd29faebe482b</t>
+          <t>https://www.indeed.com/viewjob?jk=62e0bd72df7d3118</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e0bd72df7d3118</t>
+          <t>https://www.indeed.com/viewjob?jk=198dcb2877451402</t>
         </is>
       </c>
     </row>
@@ -748,122 +748,122 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data/AI Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Meltwater</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7b2e289fa4a81b</t>
+          <t>https://www.indeed.com/viewjob?jk=85686cf3a228d676</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr AI/ML Engineer - Remote Nationwide or Hybrid in MN/DC</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Meltwater</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5428c5fe3301bb2</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7794bd20a3609e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Meltwater</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97dc64be66ad66cd</t>
+          <t>https://www.indeed.com/viewjob?jk=8ec7d4847401afbf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - AI/ML</t>
+          <t>Senior Data/AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f0117f05675ce7</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7b2e289fa4a81b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Sr AI/ML Engineer - Remote Nationwide or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f74dc1ef788e458e</t>
+          <t>https://www.indeed.com/viewjob?jk=a5428c5fe3301bb2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Machine Learning Engineer - AI/ML</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Snowflake, Dimensional Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a037ad0869b5968b</t>
+          <t>https://www.indeed.com/viewjob?jk=37f0117f05675ce7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Snowflake, Dimensional Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0b54505ba83c83</t>
+          <t>https://www.indeed.com/viewjob?jk=a037ad0869b5968b</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788be6fbb8bd5c28</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0b54505ba83c83</t>
         </is>
       </c>
     </row>
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d2969a0188cb3d</t>
+          <t>https://www.indeed.com/viewjob?jk=788be6fbb8bd5c28</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1077,11 +1077,11 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d36804ce64799b9c</t>
+          <t>https://www.indeed.com/viewjob?jk=01d2969a0188cb3d</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, ECS, RDS, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc070bfe12f04a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=32851dd10ee0e5da</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>System Engineer- Platform/API Gateway</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>O'Reilly Auto Parts</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f3ba65fc8111094</t>
+          <t>https://www.indeed.com/viewjob?jk=708d5186ef13d22a</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32851dd10ee0e5da</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab11bf9d3a0cb66</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=708d5186ef13d22a</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4179f9ef43c111</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>ArsenalTech</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,77 +1326,77 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab11bf9d3a0cb66</t>
+          <t>https://www.indeed.com/viewjob?jk=fdea458ac4b85502</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>WellBe Senior Medical</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, RDS, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4179f9ef43c111</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a2a55eff991ad8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Sr. Data Services Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Driscoll's</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Watsonville, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e07fcacb80c198</t>
+          <t>https://www.indeed.com/viewjob?jk=c8cfdb0127f0b1e9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Data Services Developer</t>
+          <t>GCP Data Eng</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Driscoll's</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Watsonville, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, RDS, Spark, Scala</t>
+          <t>GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, ETL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8cfdb0127f0b1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa07fecdad59559</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GCP Data Eng</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, ETL, Jenkins, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Spark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa07fecdad59559</t>
+          <t>https://www.indeed.com/viewjob?jk=67cc5c5d1b62b505</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Spark, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67cc5c5d1b62b505</t>
+          <t>https://www.indeed.com/viewjob?jk=cbbafc386f88b28d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior AWS Solution Architect</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Random Bit</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f8e7a290e072e8</t>
+          <t>https://www.indeed.com/viewjob?jk=27918e064eddd213</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Computer Vision</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808de345c459337e</t>
+          <t>https://www.indeed.com/viewjob?jk=62d3da9b71f09aee</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineering Specialist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Evanston, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e671763f13a7a97</t>
+          <t>https://www.indeed.com/viewjob?jk=4bd7a3f312b64eb5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - MTS</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa29de43e62d8b14</t>
+          <t>https://www.indeed.com/viewjob?jk=6e671763f13a7a97</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Software Engineer (Backend) - MTS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,42 +1676,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62f3b2380e0b366</t>
+          <t>https://www.indeed.com/viewjob?jk=aa29de43e62d8b14</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer-Architecture</t>
+          <t>Senior Machine Learning Engineer, Computer Vision</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Raiz Federal Credit Union</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2c98f7e4333c03</t>
+          <t>https://www.indeed.com/viewjob?jk=808de345c459337e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DevOps Engineer - ML &amp; Data Infrastructure</t>
+          <t>Data Engineer-Architecture</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>High 5 Games</t>
+          <t>Raiz Federal Credit Union</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b06e51cccf7a7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2c98f7e4333c03</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>DevOps Engineer - ML &amp; Data Infrastructure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>High 5 Games</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2139ccd23148ef97</t>
+          <t>https://www.indeed.com/viewjob?jk=5b06e51cccf7a7ba</t>
         </is>
       </c>
     </row>
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979fd479106b8582</t>
+          <t>https://www.indeed.com/viewjob?jk=2139ccd23148ef97</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud AWS Support Reliability Engineer (SRE)</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of New York</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Scala, Oracle</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=397e7786631910d4</t>
+          <t>https://www.indeed.com/viewjob?jk=979fd479106b8582</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Cloud AWS Support Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Federal Reserve Bank of New York</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5de3c33ef7437dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=397e7786631910d4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Senior Software Architect - Data Platform &amp; AI/ML</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Evendale, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d258aa3e235071</t>
+          <t>https://www.indeed.com/viewjob?jk=d2413d561f12c179</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Architect - Data Platform &amp; AI/ML</t>
+          <t>Senior Machine Learning Engineer (Temporary)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Brooks Running</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2413d561f12c179</t>
+          <t>https://www.indeed.com/viewjob?jk=31e77238a1b70a49</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Temporary)</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Brooks Running</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala, MLOps</t>
+          <t>RDS, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e77238a1b70a49</t>
+          <t>https://www.indeed.com/viewjob?jk=acd3a2400ded0ef7</t>
         </is>
       </c>
     </row>
@@ -2148,25 +2148,25 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>Service Delivery Center, Technology, Back End Developer, Senior</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd3a2400ded0ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6da938c8f9cc21</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Engineering Specialist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=354c512d0fde6f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4509b3b48709b4</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>WellBe Senior Medical</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Glue, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74ab129070123bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=9f1be584fe969665</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add6f4354189f849</t>
+          <t>https://www.indeed.com/viewjob?jk=0289ffc8e0d406cf</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a20b18aa66e51d2</t>
+          <t>https://www.indeed.com/viewjob?jk=74ab129070123bd2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Clayco</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fb9d94196cc44d</t>
+          <t>https://www.indeed.com/viewjob?jk=add6f4354189f849</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Periscope</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd4f1b922a309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=0a20b18aa66e51d2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Clayco</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Cloud Storage, Spark, PySpark, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d0b722ecec30e9</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fb9d94196cc44d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Periscope</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Power BI, DataOps, CI/CD, Azure DevOps, Git</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583b4c9601400970</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd4f1b922a309e4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Humbly Confident Senior Laravel Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chiro Cat</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, MySQL, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Power BI, DataOps, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d426212b47f2cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=583b4c9601400970</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Humbly Confident Senior Laravel Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Chiro Cat</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, MySQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=971c26dff07c1bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=3d426212b47f2cb5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Distributed Systems Engineer, Energy Service Engineering</t>
+          <t>Senior DevOps Engineer (AI/Cloud Modernization)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Spark Streaming, Kafka, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b311adc4e009a8c4</t>
+          <t>https://www.indeed.com/viewjob?jk=30265e60609c6fee</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Business Systems &amp; Integrations Architect</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6abc49ee6c2f3b4f</t>
+          <t>https://www.indeed.com/viewjob?jk=2682fedab4a2d801</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Forward Deployed Engineer - Applied AI - Senior - Financial Services - Consulting</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Vertex AI, Scala, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2682fedab4a2d801</t>
+          <t>https://www.indeed.com/viewjob?jk=264d256d1f44f81a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - Applied AI - Senior - Financial Services - Consulting</t>
+          <t>Senior .NET Developer - Full-time (Working from Office)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>ArsenalTech</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Vertex AI, Scala, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=264d256d1f44f81a</t>
+          <t>https://www.indeed.com/viewjob?jk=571f6ef27368da0b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer - NYC / Dallas / Los Angeles</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Portfolio BI</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e72e9173a4b1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=971c26dff07c1bdc</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Python Full Stack Developer</t>
+          <t>Sr. Distributed Systems Engineer, Energy Service Engineering</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Spark Streaming, Kafka, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f910656c4ac5af</t>
+          <t>https://www.indeed.com/viewjob?jk=b311adc4e009a8c4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Ramsey Solutions</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c5dcb3f5dd6592</t>
+          <t>https://www.indeed.com/viewjob?jk=f836a90a9a6c4031</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Full Stack Quantitative Developer - NYC / Dallas / Los Angeles</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>Portfolio BI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, BigQuery, Vertex AI, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e56c8a333352b48</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e72e9173a4b1e5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Field Engineer</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Florence HC</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f35f177eb851ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c5dcb3f5dd6592</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git</t>
+          <t>AWS, S3, GCP, BigQuery, Vertex AI, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9012b2ffe5f7c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e56c8a333352b48</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Field Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Florence HC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7fe3299d9494b8</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f35f177eb851ec</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Harbinger Motors Inc.</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1042fb894a308b35</t>
+          <t>https://www.indeed.com/viewjob?jk=d9012b2ffe5f7c5e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer II - Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL, Tableau</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15bd37695704d0b2</t>
+          <t>https://www.indeed.com/viewjob?jk=0733e6d33b962b4b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full Stack Intern</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Harbinger Motors Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Garden Grove, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e62e31febbb7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=1042fb894a308b35</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Full Stack Intern</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SQS, SNS, Hadoop, Hive, HBase, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4594ef27276bcddb</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c15d01008f879b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer – Generative AI</t>
+          <t>Full Stack Intern</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd2d5932a298301</t>
+          <t>https://www.indeed.com/viewjob?jk=15e62e31febbb7dd</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer Go Outdoors</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>SQS, SNS, Hadoop, Hive, HBase, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e38fd8d0926139</t>
+          <t>https://www.indeed.com/viewjob?jk=4594ef27276bcddb</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Platform of Greatness</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116361549f755a48</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a0aff866de84b2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SDN Automation Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Platform of Greatness</t>
+          <t>AIG</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a0aff866de84b2</t>
+          <t>https://www.indeed.com/viewjob?jk=5027122dffca8482</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - Remote -W2 Only</t>
+          <t>Senior AI/ML Full Stack Engineer – Generative AI</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Digital iTechnology</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket, Python</t>
+          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef52a4058b83ad57</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd2d5932a298301</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90f91c50a68c29bc</t>
+          <t>https://www.indeed.com/viewjob?jk=5d13c7e892b0bc19</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AI Software Engineer (Vehicle Engineering)</t>
+          <t>Software Engineer Go Outdoors</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SpaceX</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hawthorne, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad497f523694b96c</t>
+          <t>https://www.indeed.com/viewjob?jk=c6e38fd8d0926139</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Walkme</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bee16f62d775ab</t>
+          <t>https://www.indeed.com/viewjob?jk=116361549f755a48</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Full Stack Engineer - Remote -W2 Only</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Walkme</t>
+          <t>Digital iTechnology</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2363b9cbfb0252a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef52a4058b83ad57</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Walkme</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,17 +3706,52 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Kafka, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d9f2d75fa67499b</t>
+          <t>https://www.indeed.com/viewjob?jk=90f91c50a68c29bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>AI Software Engineer (Vehicle Engineering)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SpaceX</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Hawthorne, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>RDS, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad497f523694b96c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-21.xlsx
+++ b/results/job_matches_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS Data Architect</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WinWire</t>
+          <t>Ideas2IT Technologies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, RDS, Azure, GCP, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94da66580e29e534</t>
+          <t>https://www.indeed.com/viewjob?jk=65ba785f54845637</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ideas2IT Technologies</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, RDS, Azure, GCP, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65ba785f54845637</t>
+          <t>https://www.indeed.com/viewjob?jk=62e0bd72df7d3118</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e0bd72df7d3118</t>
+          <t>https://www.indeed.com/viewjob?jk=198dcb2877451402</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Spark Streaming</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198dcb2877451402</t>
+          <t>https://www.indeed.com/viewjob?jk=e9b4743d0857d2b3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Associate - AI Engineer</t>
+          <t>Data Engineer - AWS, python</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, IAM, Databricks, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cc5523e609d6490</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc48402a0ee4138</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>Senior Data/AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9b4743d0857d2b3</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7b2e289fa4a81b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS, python</t>
+          <t>Sr AI/ML Engineer - Remote Nationwide or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc48402a0ee4138</t>
+          <t>https://www.indeed.com/viewjob?jk=a5428c5fe3301bb2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer - AI/ML</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,137 +741,137 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef768a7022d9b02</t>
+          <t>https://www.indeed.com/viewjob?jk=37f0117f05675ce7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Meltwater</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Snowflake, Dimensional Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85686cf3a228d676</t>
+          <t>https://www.indeed.com/viewjob?jk=a037ad0869b5968b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Meltwater</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7794bd20a3609e</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0b54505ba83c83</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Meltwater</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ec7d4847401afbf</t>
+          <t>https://www.indeed.com/viewjob?jk=788be6fbb8bd5c28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data/AI Engineer</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7b2e289fa4a81b</t>
+          <t>https://www.indeed.com/viewjob?jk=01d2969a0188cb3d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr AI/ML Engineer - Remote Nationwide or Hybrid in MN/DC</t>
+          <t>AWS AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5428c5fe3301bb2</t>
+          <t>https://www.indeed.com/viewjob?jk=8073fabbdb00b63d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - AI/ML</t>
+          <t>Data Engineer/Sr. Data Engineer -ITDDP (Contractual)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f0117f05675ce7</t>
+          <t>https://www.indeed.com/viewjob?jk=7979c28cb86f5690</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Software Engineer – Data Engineering (GCP &amp; AI) (contract)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Snowflake, Dimensional Modeling, Kimball, ELT, dbt</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,129 +986,129 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a037ad0869b5968b</t>
+          <t>https://www.indeed.com/viewjob?jk=864bf732311fb751</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0b54505ba83c83</t>
+          <t>https://www.indeed.com/viewjob?jk=32851dd10ee0e5da</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788be6fbb8bd5c28</t>
+          <t>https://www.indeed.com/viewjob?jk=708d5186ef13d22a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d2969a0188cb3d</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab11bf9d3a0cb66</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr. Data Engineer -ITDDP (Contractual)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7979c28cb86f5690</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4179f9ef43c111</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Data Engineering (GCP &amp; AI) (contract)</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>ArsenalTech</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,209 +1151,209 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864bf732311fb751</t>
+          <t>https://www.indeed.com/viewjob?jk=fdea458ac4b85502</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>WellBe Senior Medical</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, RDS, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32851dd10ee0e5da</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a2a55eff991ad8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Services Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Driscoll's</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Watsonville, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=708d5186ef13d22a</t>
+          <t>https://www.indeed.com/viewjob?jk=c8cfdb0127f0b1e9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Data Eng</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
+          <t>GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, ETL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab11bf9d3a0cb66</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa07fecdad59559</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Dot Net Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4179f9ef43c111</t>
+          <t>https://www.indeed.com/viewjob?jk=5efceacc40589d5d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>AI Engineering Specialist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ArsenalTech</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Evanston, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdea458ac4b85502</t>
+          <t>https://www.indeed.com/viewjob?jk=4bd7a3f312b64eb5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WellBe Senior Medical</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a2a55eff991ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=cbbafc386f88b28d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Services Developer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Driscoll's</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Watsonville, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, RDS, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8cfdb0127f0b1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=27918e064eddd213</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GCP Data Eng</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, ETL, Jenkins, Jenkins</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa07fecdad59559</t>
+          <t>https://www.indeed.com/viewjob?jk=62d3da9b71f09aee</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Spark, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67cc5c5d1b62b505</t>
+          <t>https://www.indeed.com/viewjob?jk=6e671763f13a7a97</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Software Engineer (Backend) - MTS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbbafc386f88b28d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa29de43e62d8b14</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Senior Machine Learning Engineer, Computer Vision</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,112 +1536,112 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27918e064eddd213</t>
+          <t>https://www.indeed.com/viewjob?jk=808de345c459337e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer-Architecture</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Raiz Federal Credit Union</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62d3da9b71f09aee</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2c98f7e4333c03</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Engineering Specialist</t>
+          <t>DevOps Engineer - ML &amp; Data Infrastructure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>High 5 Games</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Evanston, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bd7a3f312b64eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=5b06e51cccf7a7ba</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e671763f13a7a97</t>
+          <t>https://www.indeed.com/viewjob?jk=2139ccd23148ef97</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - MTS</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa29de43e62d8b14</t>
+          <t>https://www.indeed.com/viewjob?jk=979fd479106b8582</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Computer Vision</t>
+          <t>Cloud AWS Support Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Federal Reserve Bank of New York</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808de345c459337e</t>
+          <t>https://www.indeed.com/viewjob?jk=397e7786631910d4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer-Architecture</t>
+          <t>Senior Software Engineer - Vehicle Cybersecurity</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Raiz Federal Credit Union</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,29 +1746,29 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2c98f7e4333c03</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb62768f9619d2e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps Engineer - ML &amp; Data Infrastructure</t>
+          <t>Senior Software Architect - Data Platform &amp; AI/ML</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>High 5 Games</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b06e51cccf7a7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d2413d561f12c179</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Senior Machine Learning Engineer (Temporary)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Brooks Running</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2139ccd23148ef97</t>
+          <t>https://www.indeed.com/viewjob?jk=31e77238a1b70a49</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>RDS, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979fd479106b8582</t>
+          <t>https://www.indeed.com/viewjob?jk=acd3a2400ded0ef7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud AWS Support Reliability Engineer (SRE)</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of New York</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Scala, Oracle</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=397e7786631910d4</t>
+          <t>https://www.indeed.com/viewjob?jk=a04d34ff6293d7a2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Architect - Data Platform &amp; AI/ML</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Air Today USA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Evendale, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2413d561f12c179</t>
+          <t>https://www.indeed.com/viewjob?jk=c73ef9f43ca54c71</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Temporary)</t>
+          <t>Mid-level DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Brooks Running</t>
+          <t>Ella Wholesales Coffee</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e77238a1b70a49</t>
+          <t>https://www.indeed.com/viewjob?jk=02374e2f05fa51aa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>Engineering Specialist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd3a2400ded0ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4509b3b48709b4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Service Delivery Center, Technology, Back End Developer, Senior</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a04d34ff6293d7a2</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6da938c8f9cc21</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Air Today USA</t>
+          <t>El Toro.com</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c73ef9f43ca54c71</t>
+          <t>https://www.indeed.com/viewjob?jk=c3113d217a11359b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mid-level DevOps Engineer</t>
+          <t>Platform Architect - AI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ella Wholesales Coffee</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02374e2f05fa51aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e294cc6d33384a45</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Software Engineer, Build and Release Management</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8bd188504a235ef</t>
+          <t>https://www.indeed.com/viewjob?jk=fe77948a6745c2be</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Technology, Back End Developer, Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Ideal Business Advisors</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Splunk, Docker, Kubernetes</t>
+          <t>RDS, Azure, Spark, Spark Streaming, Kafka, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6da938c8f9cc21</t>
+          <t>https://www.indeed.com/viewjob?jk=5e07e4d5100d0a09</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, MySQL, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dcc5ce5e437bc35</t>
+          <t>https://www.indeed.com/viewjob?jk=225bdb7f78f14470</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>El Toro.com</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3113d217a11359b</t>
+          <t>https://www.indeed.com/viewjob?jk=2d61f658ab71dc3d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Platform Architect - AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, S3, ECS, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,102 +2281,102 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e294cc6d33384a45</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd5378e4194090a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Build and Release Management</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>SolarWinds</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Star Schema, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe77948a6745c2be</t>
+          <t>https://www.indeed.com/viewjob?jk=1c073df0d353c1af</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Engineering Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>WellBe Senior Medical</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, Glue, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4509b3b48709b4</t>
+          <t>https://www.indeed.com/viewjob?jk=9f1be584fe969665</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ideal Business Advisors</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Spark Streaming, Kafka, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e07e4d5100d0a09</t>
+          <t>https://www.indeed.com/viewjob?jk=0289ffc8e0d406cf</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225bdb7f78f14470</t>
+          <t>https://www.indeed.com/viewjob?jk=74ab129070123bd2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d61f658ab71dc3d</t>
+          <t>https://www.indeed.com/viewjob?jk=add6f4354189f849</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB, Jenkins</t>
+          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd5378e4194090a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a20b18aa66e51d2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SolarWinds</t>
+          <t>Clayco</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Star Schema, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c073df0d353c1af</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fb9d94196cc44d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Periscope</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>WellBe Senior Medical</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f1be584fe969665</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd4f1b922a309e4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Power BI, DataOps, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0289ffc8e0d406cf</t>
+          <t>https://www.indeed.com/viewjob?jk=583b4c9601400970</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Humbly Confident Senior Laravel Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Chiro Cat</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, MySQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74ab129070123bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=3d426212b47f2cb5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Senior DevOps Engineer (AI/Cloud Modernization)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add6f4354189f849</t>
+          <t>https://www.indeed.com/viewjob?jk=30265e60609c6fee</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior .NET Developer - Full-time (Working from Office)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>ArsenalTech</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a20b18aa66e51d2</t>
+          <t>https://www.indeed.com/viewjob?jk=571f6ef27368da0b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Clayco</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fb9d94196cc44d</t>
+          <t>https://www.indeed.com/viewjob?jk=971c26dff07c1bdc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Periscope</t>
+          <t>Sr. Distributed Systems Engineer, Energy Service Engineering</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Spark Streaming, Kafka, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd4f1b922a309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=b311adc4e009a8c4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ramsey Solutions</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Power BI, DataOps, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583b4c9601400970</t>
+          <t>https://www.indeed.com/viewjob?jk=f836a90a9a6c4031</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Humbly Confident Senior Laravel Engineer</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Chiro Cat</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, MySQL, ETL, CI/CD, GitHub Actions</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d426212b47f2cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=2682fedab4a2d801</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (AI/Cloud Modernization)</t>
+          <t>Full Stack Quantitative Developer - NYC / Dallas / Los Angeles</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Portfolio BI</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30265e60609c6fee</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e72e9173a4b1e5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2682fedab4a2d801</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c5dcb3f5dd6592</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - Applied AI - Senior - Financial Services - Consulting</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Vertex AI, Scala, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, S3, GCP, BigQuery, Vertex AI, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=264d256d1f44f81a</t>
+          <t>https://www.indeed.com/viewjob?jk=5e56c8a333352b48</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior .NET Developer - Full-time (Working from Office)</t>
+          <t>Field Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ArsenalTech</t>
+          <t>Florence HC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=571f6ef27368da0b</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f35f177eb851ec</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=971c26dff07c1bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=d9012b2ffe5f7c5e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Distributed Systems Engineer, Energy Service Engineering</t>
+          <t>Forward Deployed Engineer - Applied AI - Senior - Financial Services - Consulting</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,42 +3041,42 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Spark Streaming, Kafka, ELT, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Vertex AI, Scala, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b311adc4e009a8c4</t>
+          <t>https://www.indeed.com/viewjob?jk=264d256d1f44f81a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ramsey Solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f836a90a9a6c4031</t>
+          <t>https://www.indeed.com/viewjob?jk=0733e6d33b962b4b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer - NYC / Dallas / Los Angeles</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Portfolio BI</t>
+          <t>Harbinger Motors Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Garden Grove, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e72e9173a4b1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=1042fb894a308b35</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>Full Stack Intern</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c5dcb3f5dd6592</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c15d01008f879b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Full Stack Intern</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, BigQuery, Vertex AI, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e56c8a333352b48</t>
+          <t>https://www.indeed.com/viewjob?jk=15e62e31febbb7dd</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Field Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Florence HC</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>SQS, SNS, Hadoop, Hive, HBase, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,59 +3226,59 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f35f177eb851ec</t>
+          <t>https://www.indeed.com/viewjob?jk=4594ef27276bcddb</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9012b2ffe5f7c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=ef825bd9f581fc83</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Automation Tester (AI enabled Testing)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0733e6d33b962b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=1a48d0f78302c9e9</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>SDN Automation Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Harbinger Motors Inc.</t>
+          <t>AIG</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1042fb894a308b35</t>
+          <t>https://www.indeed.com/viewjob?jk=5027122dffca8482</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full Stack Intern</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Platform of Greatness</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c15d01008f879b</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a0aff866de84b2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full Stack Intern</t>
+          <t>Senior AI/ML Full Stack Engineer – Generative AI</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e62e31febbb7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd2d5932a298301</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SQS, SNS, Hadoop, Hive, HBase, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4594ef27276bcddb</t>
+          <t>https://www.indeed.com/viewjob?jk=5d13c7e892b0bc19</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer Go Outdoors</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Platform of Greatness</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a0aff866de84b2</t>
+          <t>https://www.indeed.com/viewjob?jk=c6e38fd8d0926139</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SDN Automation Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>AIG</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5027122dffca8482</t>
+          <t>https://www.indeed.com/viewjob?jk=116361549f755a48</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer – Generative AI</t>
+          <t>Full Stack Engineer - Remote -W2 Only</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Digital iTechnology</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd2d5932a298301</t>
+          <t>https://www.indeed.com/viewjob?jk=ef52a4058b83ad57</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, RDS, Kafka, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d13c7e892b0bc19</t>
+          <t>https://www.indeed.com/viewjob?jk=90f91c50a68c29bc</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer Go Outdoors</t>
+          <t>AI Software Engineer (Vehicle Engineering)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Hawthorne, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,155 +3601,15 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e38fd8d0926139</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Quality Assurance Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>The University of Michigan</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ann Arbor, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=116361549f755a48</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer - Remote -W2 Only</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Digital iTechnology</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket, Python</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef52a4058b83ad57</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Junior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Changeis, Inc.</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Kafka, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90f91c50a68c29bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>AI Software Engineer (Vehicle Engineering)</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>SpaceX</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Hawthorne, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>RDS, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ad497f523694b96c</t>
         </is>

--- a/results/job_matches_2026-05-21.xlsx
+++ b/results/job_matches_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,87 +608,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS, python</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Mount Pleasant, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc48402a0ee4138</t>
+          <t>https://www.indeed.com/viewjob?jk=141602cced20c4a3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data/AI Engineer</t>
+          <t>Senior Database Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Dimensional Fund Advisors</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7b2e289fa4a81b</t>
+          <t>https://www.indeed.com/viewjob?jk=1ce4cdb2b3ab11fc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr AI/ML Engineer - Remote Nationwide or Hybrid in MN/DC</t>
+          <t>Senior Data/AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5428c5fe3301bb2</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7b2e289fa4a81b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - AI/ML</t>
+          <t>Sr AI/ML Engineer - Remote Nationwide or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f0117f05675ce7</t>
+          <t>https://www.indeed.com/viewjob?jk=a5428c5fe3301bb2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Machine Learning Engineer - AI/ML</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Snowflake, Dimensional Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a037ad0869b5968b</t>
+          <t>https://www.indeed.com/viewjob?jk=37f0117f05675ce7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0b54505ba83c83</t>
+          <t>https://www.indeed.com/viewjob?jk=8ce88ab29e1bd168</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Snowflake, Dimensional Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788be6fbb8bd5c28</t>
+          <t>https://www.indeed.com/viewjob?jk=a037ad0869b5968b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>Associate AI/ML Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d2969a0188cb3d</t>
+          <t>https://www.indeed.com/viewjob?jk=64afd722e7be9329</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Systems Engineer / GEOTAM / (Hybrid) [Contingent]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ArsenalTech</t>
+          <t>iWorks Corporation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Silver Spring, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,69 +1151,69 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Redshift, ECS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdea458ac4b85502</t>
+          <t>https://www.indeed.com/viewjob?jk=0e49c457532dc6f1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WellBe Senior Medical</t>
+          <t>ArsenalTech</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend</t>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a2a55eff991ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=fdea458ac4b85502</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Data Services Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Driscoll's</t>
+          <t>WellBe Senior Medical</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Watsonville, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, RDS, Spark, Scala</t>
+          <t>AWS, Glue, RDS, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8cfdb0127f0b1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a2a55eff991ad8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GCP Data Eng</t>
+          <t>Sr. Data Services Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Driscoll's</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Watsonville, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, ETL, Jenkins, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa07fecdad59559</t>
+          <t>https://www.indeed.com/viewjob?jk=c8cfdb0127f0b1e9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dot Net Engineer</t>
+          <t>GCP Data Eng</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, ETL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5efceacc40589d5d</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa07fecdad59559</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Engineering Specialist</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Evanston, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bd7a3f312b64eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=cbbafc386f88b28d</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbbafc386f88b28d</t>
+          <t>https://www.indeed.com/viewjob?jk=27918e064eddd213</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27918e064eddd213</t>
+          <t>https://www.indeed.com/viewjob?jk=62d3da9b71f09aee</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Dot Net Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62d3da9b71f09aee</t>
+          <t>https://www.indeed.com/viewjob?jk=5efceacc40589d5d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineering Specialist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Evanston, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e671763f13a7a97</t>
+          <t>https://www.indeed.com/viewjob?jk=4bd7a3f312b64eb5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - MTS</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa29de43e62d8b14</t>
+          <t>https://www.indeed.com/viewjob?jk=6e671763f13a7a97</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Computer Vision</t>
+          <t>Software Engineer (Backend) - MTS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808de345c459337e</t>
+          <t>https://www.indeed.com/viewjob?jk=aa29de43e62d8b14</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer-Architecture</t>
+          <t>Senior Machine Learning Engineer, Computer Vision</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Raiz Federal Credit Union</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2c98f7e4333c03</t>
+          <t>https://www.indeed.com/viewjob?jk=808de345c459337e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Engineer - ML &amp; Data Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>High 5 Games</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b06e51cccf7a7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=389680e185ea40c1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Data Engineer-Architecture</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Raiz Federal Credit Union</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2139ccd23148ef97</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2c98f7e4333c03</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>DevOps Engineer - ML &amp; Data Infrastructure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>High 5 Games</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979fd479106b8582</t>
+          <t>https://www.indeed.com/viewjob?jk=5b06e51cccf7a7ba</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud AWS Support Reliability Engineer (SRE)</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of New York</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Scala, Oracle</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=397e7786631910d4</t>
+          <t>https://www.indeed.com/viewjob?jk=2139ccd23148ef97</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Vehicle Cybersecurity</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb62768f9619d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=979fd479106b8582</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Architect - Data Platform &amp; AI/ML</t>
+          <t>Cloud AWS Support Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Federal Reserve Bank of New York</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2413d561f12c179</t>
+          <t>https://www.indeed.com/viewjob?jk=397e7786631910d4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Temporary)</t>
+          <t>Senior Software Engineer - Vehicle Cybersecurity</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Brooks Running</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala, MLOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e77238a1b70a49</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb62768f9619d2e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>AI/ML Engineer - Higher Ed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd3a2400ded0ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc0ea154c64d7ab</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>AI/ML Engineer - School</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a04d34ff6293d7a2</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa5fdc8e46d58c2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Oracle Cloud ERP Consultant/Functional Specialist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Air Today USA</t>
+          <t>nProspect</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,29 +1921,29 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Scala, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c73ef9f43ca54c71</t>
+          <t>https://www.indeed.com/viewjob?jk=a98b5c8606717817</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mid-level DevOps Engineer</t>
+          <t>Senior Software Architect - Data Platform &amp; AI/ML</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ella Wholesales Coffee</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02374e2f05fa51aa</t>
+          <t>https://www.indeed.com/viewjob?jk=d2413d561f12c179</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Engineering Specialist</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4509b3b48709b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a04d34ff6293d7a2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Technology, Back End Developer, Senior</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Air Today USA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Splunk, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6da938c8f9cc21</t>
+          <t>https://www.indeed.com/viewjob?jk=c73ef9f43ca54c71</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Mid-level DevOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>El Toro.com</t>
+          <t>Ella Wholesales Coffee</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3113d217a11359b</t>
+          <t>https://www.indeed.com/viewjob?jk=02374e2f05fa51aa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Platform Architect - AI</t>
+          <t>Senior Machine Learning Engineer (Temporary)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>Brooks Running</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e294cc6d33384a45</t>
+          <t>https://www.indeed.com/viewjob?jk=31e77238a1b70a49</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Build and Release Management</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe77948a6745c2be</t>
+          <t>https://www.indeed.com/viewjob?jk=acd3a2400ded0ef7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Service Delivery Center, Technology, Back End Developer, Senior</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ideal Business Advisors</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Spark Streaming, Kafka, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e07e4d5100d0a09</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6da938c8f9cc21</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>El Toro.com</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225bdb7f78f14470</t>
+          <t>https://www.indeed.com/viewjob?jk=c3113d217a11359b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Platform Architect - AI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d61f658ab71dc3d</t>
+          <t>https://www.indeed.com/viewjob?jk=e294cc6d33384a45</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineering Specialist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,77 +2271,77 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd5378e4194090a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4509b3b48709b4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SolarWinds</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Star Schema, ELT, dbt, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c073df0d353c1af</t>
+          <t>https://www.indeed.com/viewjob?jk=225bdb7f78f14470</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WellBe Senior Medical</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
+          <t>AWS, S3, ECS, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f1be584fe969665</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd5378e4194090a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>SolarWinds</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Star Schema, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0289ffc8e0d406cf</t>
+          <t>https://www.indeed.com/viewjob?jk=1c073df0d353c1af</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>WellBe Senior Medical</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Glue, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74ab129070123bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=9f1be584fe969665</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add6f4354189f849</t>
+          <t>https://www.indeed.com/viewjob?jk=0289ffc8e0d406cf</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a20b18aa66e51d2</t>
+          <t>https://www.indeed.com/viewjob?jk=74ab129070123bd2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Clayco</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fb9d94196cc44d</t>
+          <t>https://www.indeed.com/viewjob?jk=add6f4354189f849</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Periscope</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd4f1b922a309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=0a20b18aa66e51d2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Clayco</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Power BI, DataOps, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583b4c9601400970</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fb9d94196cc44d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Humbly Confident Senior Laravel Engineer</t>
+          <t>Senior Data Engineer - Periscope</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chiro Cat</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, MySQL, ETL, CI/CD, GitHub Actions</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d426212b47f2cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd4f1b922a309e4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (AI/Cloud Modernization)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Power BI, DataOps, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30265e60609c6fee</t>
+          <t>https://www.indeed.com/viewjob?jk=583b4c9601400970</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior .NET Developer - Full-time (Working from Office)</t>
+          <t>Senior DevOps Engineer (AI/Cloud Modernization)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ArsenalTech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=571f6ef27368da0b</t>
+          <t>https://www.indeed.com/viewjob?jk=30265e60609c6fee</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior .NET Developer - Full-time (Working from Office)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>ArsenalTech</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=971c26dff07c1bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=571f6ef27368da0b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Distributed Systems Engineer, Energy Service Engineering</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Spark Streaming, Kafka, ELT, CI/CD, Docker</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b311adc4e009a8c4</t>
+          <t>https://www.indeed.com/viewjob?jk=971c26dff07c1bdc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Distributed Systems Engineer, Energy Service Engineering</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ramsey Solutions</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Spark Streaming, Kafka, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f836a90a9a6c4031</t>
+          <t>https://www.indeed.com/viewjob?jk=b311adc4e009a8c4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Ramsey Solutions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2682fedab4a2d801</t>
+          <t>https://www.indeed.com/viewjob?jk=f836a90a9a6c4031</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer - NYC / Dallas / Los Angeles</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Portfolio BI</t>
+          <t>Sunikshainfotech</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e72e9173a4b1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3b306fbbf582de</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c5dcb3f5dd6592</t>
+          <t>https://www.indeed.com/viewjob?jk=2682fedab4a2d801</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Full Stack Quantitative Developer - NYC / Dallas / Los Angeles</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>Portfolio BI</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, BigQuery, Vertex AI, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e56c8a333352b48</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e72e9173a4b1e5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Field Engineer</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Florence HC</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f35f177eb851ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c5dcb3f5dd6592</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git</t>
+          <t>AWS, S3, GCP, BigQuery, Vertex AI, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9012b2ffe5f7c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e56c8a333352b48</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - Applied AI - Senior - Financial Services - Consulting</t>
+          <t>Field Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Florence HC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Vertex AI, Scala, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=264d256d1f44f81a</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f35f177eb851ec</t>
         </is>
       </c>
     </row>
@@ -3268,17 +3268,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Junior Automation Tester (AI enabled Testing)</t>
+          <t>SDN Automation Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AIG</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a48d0f78302c9e9</t>
+          <t>https://www.indeed.com/viewjob?jk=5027122dffca8482</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SDN Automation Engineer</t>
+          <t>Senior Associate - Senior AI Platform Security Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AIG</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5027122dffca8482</t>
+          <t>https://www.indeed.com/viewjob?jk=e60c5181689227fe</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Platform of Greatness</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Git</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a0aff866de84b2</t>
+          <t>https://www.indeed.com/viewjob?jk=5d13c7e892b0bc19</t>
         </is>
       </c>
     </row>
@@ -3408,17 +3408,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Software Engineer Go Outdoors</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d13c7e892b0bc19</t>
+          <t>https://www.indeed.com/viewjob?jk=c6e38fd8d0926139</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer Go Outdoors</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e38fd8d0926139</t>
+          <t>https://www.indeed.com/viewjob?jk=116361549f755a48</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Platform of Greatness</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,29 +3496,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116361549f755a48</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a0aff866de84b2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - Remote -W2 Only</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Digital iTechnology</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket, Python</t>
+          <t>AWS, RDS, Kafka, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,77 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef52a4058b83ad57</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Junior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Changeis, Inc.</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Kafka, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=90f91c50a68c29bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>AI Software Engineer (Vehicle Engineering)</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>SpaceX</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Hawthorne, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad497f523694b96c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-21.xlsx
+++ b/results/job_matches_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ideas2IT Technologies</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, RDS, Azure, GCP, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Azure, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65ba785f54845637</t>
+          <t>https://www.indeed.com/viewjob?jk=6664732c8e57da4b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Ideas2IT Technologies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, RDS, Azure, GCP, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e0bd72df7d3118</t>
+          <t>https://www.indeed.com/viewjob?jk=65ba785f54845637</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198dcb2877451402</t>
+          <t>https://www.indeed.com/viewjob?jk=62e0bd72df7d3118</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9b4743d0857d2b3</t>
+          <t>https://www.indeed.com/viewjob?jk=198dcb2877451402</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mount Pleasant, PA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141602cced20c4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=e9b4743d0857d2b3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Database Platform Engineer</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Mount Pleasant, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,42 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ce4cdb2b3ab11fc</t>
+          <t>https://www.indeed.com/viewjob?jk=141602cced20c4a3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data/AI Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
+          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7b2e289fa4a81b</t>
+          <t>https://www.indeed.com/viewjob?jk=2521221b0a4f471f</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - AI/ML</t>
+          <t>Senior Data/AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f0117f05675ce7</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7b2e289fa4a81b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer - AI/ML</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ce88ab29e1bd168</t>
+          <t>https://www.indeed.com/viewjob?jk=37f0117f05675ce7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Snowflake, Dimensional Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a037ad0869b5968b</t>
+          <t>https://www.indeed.com/viewjob?jk=eed5e5d6e7ec548f</t>
         </is>
       </c>
     </row>
@@ -888,25 +888,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8073fabbdb00b63d</t>
+          <t>https://www.indeed.com/viewjob?jk=8ce88ab29e1bd168</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr. Data Engineer -ITDDP (Contractual)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Snowflake, Dimensional Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7979c28cb86f5690</t>
+          <t>https://www.indeed.com/viewjob?jk=a037ad0869b5968b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Data Engineering (GCP &amp; AI) (contract)</t>
+          <t>AWS AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864bf732311fb751</t>
+          <t>https://www.indeed.com/viewjob?jk=8073fabbdb00b63d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer/Sr. Data Engineer -ITDDP (Contractual)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32851dd10ee0e5da</t>
+          <t>https://www.indeed.com/viewjob?jk=7979c28cb86f5690</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer – Data Engineering (GCP &amp; AI) (contract)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=708d5186ef13d22a</t>
+          <t>https://www.indeed.com/viewjob?jk=864bf732311fb751</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab11bf9d3a0cb66</t>
+          <t>https://www.indeed.com/viewjob?jk=32851dd10ee0e5da</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4179f9ef43c111</t>
+          <t>https://www.indeed.com/viewjob?jk=708d5186ef13d22a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Systems Engineer / GEOTAM / (Hybrid) [Contingent]</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>iWorks Corporation</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Silver Spring, MD, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e49c457532dc6f1</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab11bf9d3a0cb66</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ArsenalTech</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,87 +1186,87 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdea458ac4b85502</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4179f9ef43c111</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Systems Engineer / GEOTAM / (Hybrid) [Contingent]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WellBe Senior Medical</t>
+          <t>iWorks Corporation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Silver Spring, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend</t>
+          <t>AWS, Redshift, ECS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a2a55eff991ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=0e49c457532dc6f1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Data Services Developer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Driscoll's</t>
+          <t>ArsenalTech</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Watsonville, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, RDS, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8cfdb0127f0b1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=fdea458ac4b85502</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>WellBe Senior Medical</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, RDS, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbbafc386f88b28d</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a2a55eff991ad8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Sr. Data Services Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Driscoll's</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Watsonville, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27918e064eddd213</t>
+          <t>https://www.indeed.com/viewjob?jk=c8cfdb0127f0b1e9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Dot Net Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62d3da9b71f09aee</t>
+          <t>https://www.indeed.com/viewjob?jk=5efceacc40589d5d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dot Net Engineer</t>
+          <t>AI Engineering Specialist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Evanston, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,24 +1431,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5efceacc40589d5d</t>
+          <t>https://www.indeed.com/viewjob?jk=4bd7a3f312b64eb5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Engineering Specialist</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Evanston, IL, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1471,29 +1471,29 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bd7a3f312b64eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=62d3da9b71f09aee</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e671763f13a7a97</t>
+          <t>https://www.indeed.com/viewjob?jk=cbbafc386f88b28d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - MTS</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa29de43e62d8b14</t>
+          <t>https://www.indeed.com/viewjob?jk=27918e064eddd213</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Computer Vision</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808de345c459337e</t>
+          <t>https://www.indeed.com/viewjob?jk=6e671763f13a7a97</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (Backend) - MTS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389680e185ea40c1</t>
+          <t>https://www.indeed.com/viewjob?jk=aa29de43e62d8b14</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer-Architecture</t>
+          <t>Senior Machine Learning Engineer, Computer Vision</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Raiz Federal Credit Union</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2c98f7e4333c03</t>
+          <t>https://www.indeed.com/viewjob?jk=808de345c459337e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DevOps Engineer - ML &amp; Data Infrastructure</t>
+          <t>Data Engineer-Architecture</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>High 5 Games</t>
+          <t>Raiz Federal Credit Union</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b06e51cccf7a7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2c98f7e4333c03</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2139ccd23148ef97</t>
+          <t>https://www.indeed.com/viewjob?jk=d72bea8288f357ee</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979fd479106b8582</t>
+          <t>https://www.indeed.com/viewjob?jk=389680e185ea40c1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud AWS Support Reliability Engineer (SRE)</t>
+          <t>DevOps Engineer - ML &amp; Data Infrastructure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of New York</t>
+          <t>High 5 Games</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Scala, Oracle</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=397e7786631910d4</t>
+          <t>https://www.indeed.com/viewjob?jk=5b06e51cccf7a7ba</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Vehicle Cybersecurity</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb62768f9619d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=2139ccd23148ef97</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Higher Ed</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc0ea154c64d7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=979fd479106b8582</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - School</t>
+          <t>Cloud AWS Support Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>Federal Reserve Bank of New York</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa5fdc8e46d58c2</t>
+          <t>https://www.indeed.com/viewjob?jk=397e7786631910d4</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Evendale, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a04d34ff6293d7a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b48cfa32c4737ad6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - Vehicle Cybersecurity</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Air Today USA</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c73ef9f43ca54c71</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb62768f9619d2e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Mid-level DevOps Engineer</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ella Wholesales Coffee</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02374e2f05fa51aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a04d34ff6293d7a2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Temporary)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Brooks Running</t>
+          <t>Air Today USA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e77238a1b70a49</t>
+          <t>https://www.indeed.com/viewjob?jk=c73ef9f43ca54c71</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>Mid-level DevOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Ella Wholesales Coffee</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,102 +2141,102 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd3a2400ded0ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=02374e2f05fa51aa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Technology, Back End Developer, Senior</t>
+          <t>AI/ML Engineer - Higher Ed</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Splunk, Docker, Kubernetes</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6da938c8f9cc21</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc0ea154c64d7ab</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI/ML Engineer - School</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>El Toro.com</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3113d217a11359b</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa5fdc8e46d58c2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Platform Architect - AI</t>
+          <t>Senior Machine Learning Engineer (Temporary)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>Brooks Running</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e294cc6d33384a45</t>
+          <t>https://www.indeed.com/viewjob?jk=31e77238a1b70a49</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Engineering Specialist</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Endeavor Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4509b3b48709b4</t>
+          <t>https://www.indeed.com/viewjob?jk=298c4bfe00214f1f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Salesforce Developer (Hybrid/Columbia MD)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225bdb7f78f14470</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfd9cd9ac48b12f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Service Delivery Center, Technology, Back End Developer, Senior</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,102 +2351,102 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd5378e4194090a</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6da938c8f9cc21</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SolarWinds</t>
+          <t>El Toro.com</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Star Schema, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c073df0d353c1af</t>
+          <t>https://www.indeed.com/viewjob?jk=c3113d217a11359b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineering Specialist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WellBe Senior Medical</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f1be584fe969665</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4509b3b48709b4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0289ffc8e0d406cf</t>
+          <t>https://www.indeed.com/viewjob?jk=225bdb7f78f14470</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Platform Architect - AI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74ab129070123bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=e294cc6d33384a45</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, S3, ECS, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add6f4354189f849</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd5378e4194090a</t>
         </is>
       </c>
     </row>
@@ -2538,12 +2538,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Power BI, DataOps, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a20b18aa66e51d2</t>
+          <t>https://www.indeed.com/viewjob?jk=583b4c9601400970</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Clayco</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fb9d94196cc44d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a20b18aa66e51d2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Periscope</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>SolarWinds</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Star Schema, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd4f1b922a309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=1c073df0d353c1af</t>
         </is>
       </c>
     </row>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>WellBe Senior Medical</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Power BI, DataOps, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Glue, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583b4c9601400970</t>
+          <t>https://www.indeed.com/viewjob?jk=9f1be584fe969665</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (AI/Cloud Modernization)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30265e60609c6fee</t>
+          <t>https://www.indeed.com/viewjob?jk=0289ffc8e0d406cf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior .NET Developer - Full-time (Working from Office)</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ArsenalTech</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=571f6ef27368da0b</t>
+          <t>https://www.indeed.com/viewjob?jk=74ab129070123bd2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=971c26dff07c1bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=add6f4354189f849</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Distributed Systems Engineer, Energy Service Engineering</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Clayco</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Spark Streaming, Kafka, ELT, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b311adc4e009a8c4</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fb9d94196cc44d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior System Engineering - Engineering Operations</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ramsey Solutions</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>API Gateway, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f836a90a9a6c4031</t>
+          <t>https://www.indeed.com/viewjob?jk=cda7123f0312159f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sunikshainfotech</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, CI/CD, Jenkins, Docker</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3b306fbbf582de</t>
+          <t>https://www.indeed.com/viewjob?jk=971c26dff07c1bdc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,29 +2901,29 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2682fedab4a2d801</t>
+          <t>https://www.indeed.com/viewjob?jk=79da7babfe0a8608</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer - NYC / Dallas / Los Angeles</t>
+          <t>Senior DevOps Engineer (AI/Cloud Modernization)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Portfolio BI</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e72e9173a4b1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=30265e60609c6fee</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Ramsey Solutions</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c5dcb3f5dd6592</t>
+          <t>https://www.indeed.com/viewjob?jk=f836a90a9a6c4031</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>Sunikshainfotech</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, BigQuery, Vertex AI, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e56c8a333352b48</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3b306fbbf582de</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Field Engineer</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Florence HC</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f35f177eb851ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c5dcb3f5dd6592</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,67 +3086,67 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0733e6d33b962b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=2682fedab4a2d801</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Senior .NET Developer - Full-time (Working from Office)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Harbinger Motors Inc.</t>
+          <t>ArsenalTech</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1042fb894a308b35</t>
+          <t>https://www.indeed.com/viewjob?jk=571f6ef27368da0b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack Intern</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, GCP, BigQuery, Vertex AI, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c15d01008f879b</t>
+          <t>https://www.indeed.com/viewjob?jk=5e56c8a333352b48</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Intern</t>
+          <t>Field Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Florence HC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e62e31febbb7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f35f177eb851ec</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SQS, SNS, Hadoop, Hive, HBase, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4594ef27276bcddb</t>
+          <t>https://www.indeed.com/viewjob?jk=0733e6d33b962b4b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Full Stack Intern</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef825bd9f581fc83</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c15d01008f879b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SDN Automation Engineer</t>
+          <t>Full Stack Intern</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AIG</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5027122dffca8482</t>
+          <t>https://www.indeed.com/viewjob?jk=15e62e31febbb7dd</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Associate - Senior AI Platform Security Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>SQS, SNS, Hadoop, Hive, HBase, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60c5181689227fe</t>
+          <t>https://www.indeed.com/viewjob?jk=4594ef27276bcddb</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Harbinger Motors Inc.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Garden Grove, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d13c7e892b0bc19</t>
+          <t>https://www.indeed.com/viewjob?jk=1042fb894a308b35</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer – Generative AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd2d5932a298301</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d57f388e905047</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer Go Outdoors</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e38fd8d0926139</t>
+          <t>https://www.indeed.com/viewjob?jk=5d13c7e892b0bc19</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>SDN Automation Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>AIG</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116361549f755a48</t>
+          <t>https://www.indeed.com/viewjob?jk=5027122dffca8482</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI/ML Full Stack Engineer – Generative AI</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Platform of Greatness</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Git</t>
+          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a0aff866de84b2</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd2d5932a298301</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Software Engineer Go Outdoors</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,15 +3531,155 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6e38fd8d0926139</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Associate - Senior AI Platform Security Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>New York Life</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e60c5181689227fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, PySpark, Scala, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef825bd9f581fc83</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Platform of Greatness</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3a0aff866de84b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Changeis, Inc.</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>AWS, RDS, Kafka, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=90f91c50a68c29bc</t>
         </is>

--- a/results/job_matches_2026-05-21.xlsx
+++ b/results/job_matches_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Sr. Marketing Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ideas2IT Technologies</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, RDS, Azure, GCP, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65ba785f54845637</t>
+          <t>https://www.indeed.com/viewjob?jk=1a9d4be577548066</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Ideas2IT Technologies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,17 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, RDS, Azure, GCP, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e0bd72df7d3118</t>
+          <t>https://www.indeed.com/viewjob?jk=65ba785f54845637</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>AWS Dev Ops Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9b4743d0857d2b3</t>
+          <t>https://www.indeed.com/viewjob?jk=42661b3f734ffd01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mount Pleasant, PA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141602cced20c4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=e9b4743d0857d2b3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Mount Pleasant, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,94 +706,94 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2521221b0a4f471f</t>
+          <t>https://www.indeed.com/viewjob?jk=141602cced20c4a3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr AI/ML Engineer - Remote Nationwide or Hybrid in MN/DC</t>
+          <t>Data Engineer V</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Planet DDS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5428c5fe3301bb2</t>
+          <t>https://www.indeed.com/viewjob?jk=b3fecef5d75ec74d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data/AI Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
+          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7b2e289fa4a81b</t>
+          <t>https://www.indeed.com/viewjob?jk=2521221b0a4f471f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - AI/ML</t>
+          <t>Senior Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,104 +801,104 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+          <t>AWS, Lambda, Step Functions, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f0117f05675ce7</t>
+          <t>https://www.indeed.com/viewjob?jk=b8220b39cfe7da8f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr AI/ML Engineer - Remote Nationwide or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed5e5d6e7ec548f</t>
+          <t>https://www.indeed.com/viewjob?jk=a5428c5fe3301bb2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate AI/ML Engineer</t>
+          <t>Senior Machine Learning Engineer - AI/ML</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64afd722e7be9329</t>
+          <t>https://www.indeed.com/viewjob?jk=37f0117f05675ce7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ce88ab29e1bd168</t>
+          <t>https://www.indeed.com/viewjob?jk=eed5e5d6e7ec548f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Associate AI/ML Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Snowflake, Dimensional Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a037ad0869b5968b</t>
+          <t>https://www.indeed.com/viewjob?jk=64afd722e7be9329</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AWS AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8073fabbdb00b63d</t>
+          <t>https://www.indeed.com/viewjob?jk=8ce88ab29e1bd168</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr. Data Engineer -ITDDP (Contractual)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Snowflake, Dimensional Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7979c28cb86f5690</t>
+          <t>https://www.indeed.com/viewjob?jk=a037ad0869b5968b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Data Engineering (GCP &amp; AI) (contract)</t>
+          <t>AWS AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864bf732311fb751</t>
+          <t>https://www.indeed.com/viewjob?jk=8073fabbdb00b63d</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ArsenalTech</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdea458ac4b85502</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a79496f7a592b2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GCP Data Eng</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>WellBe Senior Medical</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, ETL, Jenkins, Jenkins</t>
+          <t>AWS, Glue, RDS, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa07fecdad59559</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a2a55eff991ad8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Services Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WellBe Senior Medical</t>
+          <t>Driscoll's</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Watsonville, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a2a55eff991ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=c8cfdb0127f0b1e9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Services Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Driscoll's</t>
+          <t>AmpliFI Loyalty Solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Watsonville, CA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, RDS, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8cfdb0127f0b1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=63d5413692a768ae</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Engineering Specialist</t>
+          <t>Senior Software Engineer - Landmark</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Evanston, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,24 +1431,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bd7a3f312b64eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=0b70ae077b21d43d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Engineering Specialist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Evanston, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1471,29 +1471,29 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62d3da9b71f09aee</t>
+          <t>https://www.indeed.com/viewjob?jk=4bd7a3f312b64eb5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbbafc386f88b28d</t>
+          <t>https://www.indeed.com/viewjob?jk=62d3da9b71f09aee</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27918e064eddd213</t>
+          <t>https://www.indeed.com/viewjob?jk=cbbafc386f88b28d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e671763f13a7a97</t>
+          <t>https://www.indeed.com/viewjob?jk=27918e064eddd213</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - MTS</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa29de43e62d8b14</t>
+          <t>https://www.indeed.com/viewjob?jk=6e671763f13a7a97</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Computer Vision</t>
+          <t>AI/ML Engineer Remote Nationwide or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808de345c459337e</t>
+          <t>https://www.indeed.com/viewjob?jk=50d98338c0227a30</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72bea8288f357ee</t>
+          <t>https://www.indeed.com/viewjob?jk=31c88ead1771c841</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389680e185ea40c1</t>
+          <t>https://www.indeed.com/viewjob?jk=d72bea8288f357ee</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps Engineer - ML &amp; Data Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>High 5 Games</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b06e51cccf7a7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=389680e185ea40c1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>DevOps Engineer - ML &amp; Data Infrastructure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>High 5 Games</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2139ccd23148ef97</t>
+          <t>https://www.indeed.com/viewjob?jk=5b06e51cccf7a7ba</t>
         </is>
       </c>
     </row>
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979fd479106b8582</t>
+          <t>https://www.indeed.com/viewjob?jk=2139ccd23148ef97</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud AWS Support Reliability Engineer (SRE)</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of New York</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Scala, Oracle</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=397e7786631910d4</t>
+          <t>https://www.indeed.com/viewjob?jk=979fd479106b8582</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Oracle Cloud ERP Consultant/Functional Specialist</t>
+          <t>Cloud AWS Support Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nProspect</t>
+          <t>Federal Reserve Bank of New York</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a98b5c8606717817</t>
+          <t>https://www.indeed.com/viewjob?jk=397e7786631910d4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Architect - Data Platform &amp; AI/ML</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Evendale, OH, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2413d561f12c179</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6664a8282197f8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Integrations Architect- Azure</t>
+          <t>Oracle Cloud ERP Consultant/Functional Specialist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>nProspect</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Scala, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b48cfa32c4737ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=a98b5c8606717817</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Vehicle Cybersecurity</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb62768f9619d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=b48cfa32c4737ad6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>MCG Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a04d34ff6293d7a2</t>
+          <t>https://www.indeed.com/viewjob?jk=182cec56d83888e9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Air Today USA</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c73ef9f43ca54c71</t>
+          <t>https://www.indeed.com/viewjob?jk=a04d34ff6293d7a2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mid-level DevOps Engineer</t>
+          <t>Senior Software Architect - Data Platform &amp; AI/ML</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ella Wholesales Coffee</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Evendale, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02374e2f05fa51aa</t>
+          <t>https://www.indeed.com/viewjob?jk=d2413d561f12c179</t>
         </is>
       </c>
     </row>
@@ -2218,52 +2218,52 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Temporary)</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Brooks Running</t>
+          <t>Endeavor Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala, MLOps</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e77238a1b70a49</t>
+          <t>https://www.indeed.com/viewjob?jk=298c4bfe00214f1f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Salesforce Developer (Hybrid/Columbia MD)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Endeavor Health</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298c4bfe00214f1f</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfd9cd9ac48b12f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Salesforce Developer (Hybrid/Columbia MD)</t>
+          <t>Service Delivery Center, Technology, Back End Developer, Senior</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfd9cd9ac48b12f</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6da938c8f9cc21</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Technology, Back End Developer, Senior</t>
+          <t>Engineering Specialist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Splunk, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6da938c8f9cc21</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4509b3b48709b4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior DevSecOps Platform Engineer, AI Automation</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>El Toro.com</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3113d217a11359b</t>
+          <t>https://www.indeed.com/viewjob?jk=d56f369e5dbe7882</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Engineering Specialist</t>
+          <t>Data Scientist Stf</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Leidos QTC Health Services</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, Lambda, S3, RDS, Spark, PySpark, Scala, NoSQL, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4509b3b48709b4</t>
+          <t>https://www.indeed.com/viewjob?jk=39de61bacf1d31b2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>El Toro.com</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225bdb7f78f14470</t>
+          <t>https://www.indeed.com/viewjob?jk=c3113d217a11359b</t>
         </is>
       </c>
     </row>
@@ -2498,25 +2498,25 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Power BI, DataOps, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd5378e4194090a</t>
+          <t>https://www.indeed.com/viewjob?jk=583b4c9601400970</t>
         </is>
       </c>
     </row>
@@ -2538,12 +2538,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Power BI, DataOps, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583b4c9601400970</t>
+          <t>https://www.indeed.com/viewjob?jk=0a20b18aa66e51d2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Foundations)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a20b18aa66e51d2</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6fe26cff174d95</t>
         </is>
       </c>
     </row>
@@ -2883,17 +2883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Symmetry Lending</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,19 +2911,19 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79da7babfe0a8608</t>
+          <t>https://www.indeed.com/viewjob?jk=1422b190c43693a0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (AI/Cloud Modernization)</t>
+          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30265e60609c6fee</t>
+          <t>https://www.indeed.com/viewjob?jk=79da7babfe0a8608</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>Senior DevOps Engineer (AI/Cloud Modernization)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c5dcb3f5dd6592</t>
+          <t>https://www.indeed.com/viewjob?jk=30265e60609c6fee</t>
         </is>
       </c>
     </row>
@@ -3163,25 +3163,25 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Field Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Florence HC</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f35f177eb851ec</t>
+          <t>https://www.indeed.com/viewjob?jk=0733e6d33b962b4b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Intern</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0733e6d33b962b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c15d01008f879b</t>
         </is>
       </c>
     </row>
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c15d01008f879b</t>
+          <t>https://www.indeed.com/viewjob?jk=15e62e31febbb7dd</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full Stack Intern</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Harbinger Motors Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Garden Grove, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e62e31febbb7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=1042fb894a308b35</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SQS, SNS, Hadoop, Hive, HBase, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4594ef27276bcddb</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d57f388e905047</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Harbinger Motors Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1042fb894a308b35</t>
+          <t>https://www.indeed.com/viewjob?jk=5d13c7e892b0bc19</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SDN Automation Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>AIG</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d57f388e905047</t>
+          <t>https://www.indeed.com/viewjob?jk=5027122dffca8482</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Senior AI/ML Full Stack Engineer – Generative AI</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d13c7e892b0bc19</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd2d5932a298301</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SDN Automation Engineer</t>
+          <t>Senior Associate - Senior AI Platform Security Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AIG</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5027122dffca8482</t>
+          <t>https://www.indeed.com/viewjob?jk=e60c5181689227fe</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer – Generative AI</t>
+          <t>Sr. Software Engineer, Threat Intelligence</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Proofpoint</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, SQS, SNS, ECS, RDS, PostgreSQL, CI/CD, GitHub Actions, Docker, AKS</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd2d5932a298301</t>
+          <t>https://www.indeed.com/viewjob?jk=7b6f6e39a72c1b8e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer Go Outdoors</t>
+          <t>Data Platform Engineer – Alteryx Platform Owner / Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MongoDB, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e38fd8d0926139</t>
+          <t>https://www.indeed.com/viewjob?jk=61d632e85736717d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Associate - Senior AI Platform Security Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Platform of Greatness</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60c5181689227fe</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a0aff866de84b2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Software Engineer Go Outdoors</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef825bd9f581fc83</t>
+          <t>https://www.indeed.com/viewjob?jk=c6e38fd8d0926139</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Platform of Greatness</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,50 +3636,15 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Git</t>
+          <t>AWS, RDS, Kafka, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a0aff866de84b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Junior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Changeis, Inc.</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Kafka, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=90f91c50a68c29bc</t>
         </is>

--- a/results/job_matches_2026-05-21.xlsx
+++ b/results/job_matches_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,87 +538,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ideas2IT Technologies</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, RDS, Azure, GCP, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65ba785f54845637</t>
+          <t>https://www.indeed.com/viewjob?jk=198dcb2877451402</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Dev Ops Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198dcb2877451402</t>
+          <t>https://www.indeed.com/viewjob?jk=42661b3f734ffd01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Dev Ops Engineer (Hybrid)</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hive, Spark, Scala</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42661b3f734ffd01</t>
+          <t>https://www.indeed.com/viewjob?jk=e9b4743d0857d2b3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Mount Pleasant, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9b4743d0857d2b3</t>
+          <t>https://www.indeed.com/viewjob?jk=141602cced20c4a3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Data Engineer V</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Planet DDS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mount Pleasant, PA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141602cced20c4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=b3fecef5d75ec74d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer V</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Planet DDS</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3fecef5d75ec74d</t>
+          <t>https://www.indeed.com/viewjob?jk=2521221b0a4f471f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Step Functions, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2521221b0a4f471f</t>
+          <t>https://www.indeed.com/viewjob?jk=b8220b39cfe7da8f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Architect, Software Engineering</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8220b39cfe7da8f</t>
+          <t>https://www.indeed.com/viewjob?jk=eed5e5d6e7ec548f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr AI/ML Engineer - Remote Nationwide or Hybrid in MN/DC</t>
+          <t>Associate AI/ML Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -832,73 +832,73 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5428c5fe3301bb2</t>
+          <t>https://www.indeed.com/viewjob?jk=64afd722e7be9329</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - AI/ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f0117f05675ce7</t>
+          <t>https://www.indeed.com/viewjob?jk=8ce88ab29e1bd168</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Snowflake, Dimensional Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed5e5d6e7ec548f</t>
+          <t>https://www.indeed.com/viewjob?jk=a037ad0869b5968b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Associate AI/ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Boston Energy Trading and Marketing</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64afd722e7be9329</t>
+          <t>https://www.indeed.com/viewjob?jk=67ecc5a6b05e7ef0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ce88ab29e1bd168</t>
+          <t>https://www.indeed.com/viewjob?jk=8073fabbdb00b63d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Snowflake, Dimensional Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a037ad0869b5968b</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a79496f7a592b2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AWS AI Engineer</t>
+          <t>Systems Engineer / GEOTAM / (Hybrid) [Contingent]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>iWorks Corporation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Silver Spring, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Redshift, ECS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,172 +1056,172 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8073fabbdb00b63d</t>
+          <t>https://www.indeed.com/viewjob?jk=0e49c457532dc6f1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>WellBe Senior Medical</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, RDS, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32851dd10ee0e5da</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a2a55eff991ad8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Services Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Driscoll's</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Watsonville, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=708d5186ef13d22a</t>
+          <t>https://www.indeed.com/viewjob?jk=c8cfdb0127f0b1e9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>AmpliFI Loyalty Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab11bf9d3a0cb66</t>
+          <t>https://www.indeed.com/viewjob?jk=63d5413692a768ae</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4179f9ef43c111</t>
+          <t>https://www.indeed.com/viewjob?jk=d5883ce98bd3b809</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Systems Engineer / GEOTAM / (Hybrid) [Contingent]</t>
+          <t>Dot Net Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>iWorks Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Silver Spring, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,59 +1231,59 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e49c457532dc6f1</t>
+          <t>https://www.indeed.com/viewjob?jk=5efceacc40589d5d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Software Engineer - Landmark</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a79496f7a592b2</t>
+          <t>https://www.indeed.com/viewjob?jk=0b70ae077b21d43d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineering Specialist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WellBe Senior Medical</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Evanston, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a2a55eff991ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=4bd7a3f312b64eb5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Data Services Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Driscoll's</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Watsonville, CA, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, RDS, Spark, Scala</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8cfdb0127f0b1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=62d3da9b71f09aee</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AmpliFI Loyalty Solutions</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d5413692a768ae</t>
+          <t>https://www.indeed.com/viewjob?jk=cbbafc386f88b28d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dot Net Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5efceacc40589d5d</t>
+          <t>https://www.indeed.com/viewjob?jk=27918e064eddd213</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Landmark</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b70ae077b21d43d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e671763f13a7a97</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Engineering Specialist</t>
+          <t>AI/ML Engineer Remote Nationwide or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Evanston, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,77 +1466,77 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, API Gateway, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bd7a3f312b64eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=50d98338c0227a30</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer-Architecture</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Raiz Federal Credit Union</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62d3da9b71f09aee</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2c98f7e4333c03</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbbafc386f88b28d</t>
+          <t>https://www.indeed.com/viewjob?jk=31c88ead1771c841</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,94 +1581,94 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27918e064eddd213</t>
+          <t>https://www.indeed.com/viewjob?jk=d72bea8288f357ee</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e671763f13a7a97</t>
+          <t>https://www.indeed.com/viewjob?jk=389680e185ea40c1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Remote Nationwide or Hybrid in MN/DC</t>
+          <t>DevOps Engineer - ML &amp; Data Infrastructure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>High 5 Games</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d98338c0227a30</t>
+          <t>https://www.indeed.com/viewjob?jk=5b06e51cccf7a7ba</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer-Architecture</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Raiz Federal Credit Union</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2c98f7e4333c03</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6664a8282197f8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Oracle Cloud ERP Consultant/Functional Specialist</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>nProspect</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c88ead1771c841</t>
+          <t>https://www.indeed.com/viewjob?jk=a98b5c8606717817</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72bea8288f357ee</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dbf1260c7d0cc0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389680e185ea40c1</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b1713c37555cdd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DevOps Engineer - ML &amp; Data Infrastructure</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>High 5 Games</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b06e51cccf7a7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d440e3e598ce5c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2139ccd23148ef97</t>
+          <t>https://www.indeed.com/viewjob?jk=b48cfa32c4737ad6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>MCG Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979fd479106b8582</t>
+          <t>https://www.indeed.com/viewjob?jk=182cec56d83888e9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud AWS Support Reliability Engineer (SRE)</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of New York</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Scala, Oracle</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=397e7786631910d4</t>
+          <t>https://www.indeed.com/viewjob?jk=a04d34ff6293d7a2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Architect - Data Platform &amp; AI/ML</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Evendale, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6664a8282197f8</t>
+          <t>https://www.indeed.com/viewjob?jk=d2413d561f12c179</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Oracle Cloud ERP Consultant/Functional Specialist</t>
+          <t>AI/ML Engineer - Higher Ed</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nProspect</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a98b5c8606717817</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc0ea154c64d7ab</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Integrations Architect- Azure</t>
+          <t>AI/ML Engineer - School</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,29 +2026,29 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b48cfa32c4737ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa5fdc8e46d58c2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MCG Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2057,11 +2057,11 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,102 +2071,102 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=182cec56d83888e9</t>
+          <t>https://www.indeed.com/viewjob?jk=7ebda74063a09351</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Analyst - Data Engineering 5A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a04d34ff6293d7a2</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d7974c7f716d89</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Architect - Data Platform &amp; AI/ML</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Endeavor Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Evendale, OH, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2413d561f12c179</t>
+          <t>https://www.indeed.com/viewjob?jk=298c4bfe00214f1f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Higher Ed</t>
+          <t>Data Architect - Advanced</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc0ea154c64d7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=2598e893f85ae2a1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - School</t>
+          <t>Salesforce Developer (Hybrid/Columbia MD)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa5fdc8e46d58c2</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfd9cd9ac48b12f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Engineering Specialist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Endeavor Health</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298c4bfe00214f1f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4509b3b48709b4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Salesforce Developer (Hybrid/Columbia MD)</t>
+          <t>Senior DevSecOps Platform Engineer, AI Automation</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfd9cd9ac48b12f</t>
+          <t>https://www.indeed.com/viewjob?jk=d56f369e5dbe7882</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Engineering Specialist</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>El Toro.com</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,77 +2341,77 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4509b3b48709b4</t>
+          <t>https://www.indeed.com/viewjob?jk=c3113d217a11359b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Platform Engineer, AI Automation</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Power BI, DataOps, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56f369e5dbe7882</t>
+          <t>https://www.indeed.com/viewjob?jk=583b4c9601400970</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Scientist Stf</t>
+          <t>Senior Data Engineer (Foundations)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Leidos QTC Health Services</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Spark, PySpark, Scala, NoSQL, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39de61bacf1d31b2</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6fe26cff174d95</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>El Toro.com</t>
+          <t>SolarWinds</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Star Schema, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3113d217a11359b</t>
+          <t>https://www.indeed.com/viewjob?jk=1c073df0d353c1af</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Platform Architect - AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>WellBe Senior Medical</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, Glue, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e294cc6d33384a45</t>
+          <t>https://www.indeed.com/viewjob?jk=9f1be584fe969665</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Power BI, DataOps, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583b4c9601400970</t>
+          <t>https://www.indeed.com/viewjob?jk=0289ffc8e0d406cf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a20b18aa66e51d2</t>
+          <t>https://www.indeed.com/viewjob?jk=74ab129070123bd2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Foundations)</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6fe26cff174d95</t>
+          <t>https://www.indeed.com/viewjob?jk=add6f4354189f849</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Architect - Intermediate</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SolarWinds</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Star Schema, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c073df0d353c1af</t>
+          <t>https://www.indeed.com/viewjob?jk=53a36f9ca1924521</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior System Engineering - Engineering Operations</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WellBe Senior Medical</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
+          <t>API Gateway, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f1be584fe969665</t>
+          <t>https://www.indeed.com/viewjob?jk=cda7123f0312159f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0289ffc8e0d406cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c99ee79a934f0166</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74ab129070123bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=597ef21a1e4293fd</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add6f4354189f849</t>
+          <t>https://www.indeed.com/viewjob?jk=5a92c59262b56cdb</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Clayco</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fb9d94196cc44d</t>
+          <t>https://www.indeed.com/viewjob?jk=92b862d92b1cbb9d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior System Engineering - Engineering Operations</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Symmetry Lending</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cda7123f0312159f</t>
+          <t>https://www.indeed.com/viewjob?jk=1422b190c43693a0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=971c26dff07c1bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=79da7babfe0a8608</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Symmetry Lending</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1422b190c43693a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ae21c352f885d87b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Ramsey Solutions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79da7babfe0a8608</t>
+          <t>https://www.indeed.com/viewjob?jk=f836a90a9a6c4031</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ramsey Solutions</t>
+          <t>Sunikshainfotech</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f836a90a9a6c4031</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3b306fbbf582de</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sunikshainfotech</t>
+          <t>Vantive</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, CI/CD, Jenkins, Docker</t>
+          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3b306fbbf582de</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4303a949ff0206</t>
         </is>
       </c>
     </row>
@@ -3128,17 +3128,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, BigQuery, Vertex AI, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e56c8a333352b48</t>
+          <t>https://www.indeed.com/viewjob?jk=971c26dff07c1bdc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, S3, GCP, BigQuery, Vertex AI, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0733e6d33b962b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=5e56c8a333352b48</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full Stack Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c15d01008f879b</t>
+          <t>https://www.indeed.com/viewjob?jk=0733e6d33b962b4b</t>
         </is>
       </c>
     </row>
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e62e31febbb7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c15d01008f879b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Full Stack Intern</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Harbinger Motors Inc.</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1042fb894a308b35</t>
+          <t>https://www.indeed.com/viewjob?jk=15e62e31febbb7dd</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Harbinger Motors Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Garden Grove, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d57f388e905047</t>
+          <t>https://www.indeed.com/viewjob?jk=1042fb894a308b35</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Sr. Data Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Octapharma</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d13c7e892b0bc19</t>
+          <t>https://www.indeed.com/viewjob?jk=e4dc84fd3a2c0c7c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SDN Automation Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AIG</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5027122dffca8482</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d57f388e905047</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer – Generative AI</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd2d5932a298301</t>
+          <t>https://www.indeed.com/viewjob?jk=5d13c7e892b0bc19</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Associate - Senior AI Platform Security Engineer</t>
+          <t>SDN Automation Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>AIG</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60c5181689227fe</t>
+          <t>https://www.indeed.com/viewjob?jk=5027122dffca8482</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Threat Intelligence</t>
+          <t>Senior Associate - Senior AI Platform Security Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, PostgreSQL, CI/CD, GitHub Actions, Docker, AKS</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b6f6e39a72c1b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=e60c5181689227fe</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Platform Engineer – Alteryx Platform Owner / Engineer</t>
+          <t>Sr. Software Engineer, Threat Intelligence</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Proofpoint</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MongoDB, Jenkins, Maven, Jenkins</t>
+          <t>AWS, SQS, SNS, ECS, RDS, PostgreSQL, CI/CD, GitHub Actions, Docker, AKS</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d632e85736717d</t>
+          <t>https://www.indeed.com/viewjob?jk=7b6f6e39a72c1b8e</t>
         </is>
       </c>
     </row>
@@ -3583,17 +3583,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer Go Outdoors</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Kafka, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e38fd8d0926139</t>
+          <t>https://www.indeed.com/viewjob?jk=90f91c50a68c29bc</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior AI/ML Full Stack Engineer – Generative AI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,42 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90f91c50a68c29bc</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd2d5932a298301</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer – Alteryx Platform Owner / Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MongoDB, Jenkins, Maven, Jenkins</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61d632e85736717d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-21.xlsx
+++ b/results/job_matches_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Data Engineer V</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Planet DDS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mount Pleasant, PA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141602cced20c4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=b3fecef5d75ec74d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer V</t>
+          <t>Senior Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Planet DDS</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3fecef5d75ec74d</t>
+          <t>https://www.indeed.com/viewjob?jk=d8824834cc316357</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Boston Energy Trading and Marketing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ce88ab29e1bd168</t>
+          <t>https://www.indeed.com/viewjob?jk=67ecc5a6b05e7ef0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Snowflake, Dimensional Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a037ad0869b5968b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ce88ab29e1bd168</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Boston Energy Trading and Marketing</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Snowflake, Dimensional Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ecc5a6b05e7ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=a037ad0869b5968b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AWS AI Engineer</t>
+          <t>Intermediate Quality Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8073fabbdb00b63d</t>
+          <t>https://www.indeed.com/viewjob?jk=559ccb02cb7d178f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AWS AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a79496f7a592b2</t>
+          <t>https://www.indeed.com/viewjob?jk=8073fabbdb00b63d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Systems Engineer / GEOTAM / (Hybrid) [Contingent]</t>
+          <t>Platform Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>iWorks Corporation</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Silver Spring, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,94 +1056,94 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e49c457532dc6f1</t>
+          <t>https://www.indeed.com/viewjob?jk=0950591f503ca967</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WellBe Senior Medical</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a2a55eff991ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a79496f7a592b2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Data Services Developer</t>
+          <t>Systems Engineer / GEOTAM / (Hybrid) [Contingent]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Driscoll's</t>
+          <t>iWorks Corporation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Watsonville, CA, US USA</t>
+          <t>Silver Spring, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, RDS, Spark, Scala</t>
+          <t>AWS, Redshift, ECS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8cfdb0127f0b1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=0e49c457532dc6f1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AmpliFI Loyalty Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Databricks, Data Lake Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d5413692a768ae</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa2a5e5e0026531</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dot Net Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>WellBe Senior Medical</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5efceacc40589d5d</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a2a55eff991ad8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Landmark</t>
+          <t>Sr. Data Services Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Driscoll's</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Watsonville, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b70ae077b21d43d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8cfdb0127f0b1e9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Engineering Specialist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>AmpliFI Loyalty Solutions</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Evanston, IL, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bd7a3f312b64eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=63d5413692a768ae</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer - Landmark</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62d3da9b71f09aee</t>
+          <t>https://www.indeed.com/viewjob?jk=0b70ae077b21d43d</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Remote Nationwide or Hybrid in MN/DC</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,69 +1466,69 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d98338c0227a30</t>
+          <t>https://www.indeed.com/viewjob?jk=62d3da9b71f09aee</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer-Architecture</t>
+          <t>AI/ML Engineer Remote Nationwide or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Raiz Federal Credit Union</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, API Gateway, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2c98f7e4333c03</t>
+          <t>https://www.indeed.com/viewjob?jk=50d98338c0227a30</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Engineer-Architecture</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Raiz Federal Credit Union</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c88ead1771c841</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2c98f7e4333c03</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72bea8288f357ee</t>
+          <t>https://www.indeed.com/viewjob?jk=31c88ead1771c841</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389680e185ea40c1</t>
+          <t>https://www.indeed.com/viewjob?jk=d72bea8288f357ee</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DevOps Engineer - ML &amp; Data Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>High 5 Games</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b06e51cccf7a7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=389680e185ea40c1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer - ML &amp; Data Infrastructure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>High 5 Games</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6664a8282197f8</t>
+          <t>https://www.indeed.com/viewjob?jk=5b06e51cccf7a7ba</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Oracle Cloud ERP Consultant/Functional Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nProspect</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a98b5c8606717817</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6664a8282197f8</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>AI/ML Engineer - Higher Ed</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a04d34ff6293d7a2</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc0ea154c64d7ab</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Architect - Data Platform &amp; AI/ML</t>
+          <t>AI/ML Engineer - School</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Evendale, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2413d561f12c179</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa5fdc8e46d58c2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Higher Ed</t>
+          <t>Senior Software Architect - Data Platform &amp; AI/ML</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Evendale, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc0ea154c64d7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=d2413d561f12c179</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - School</t>
+          <t>Sr Data Quality Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa5fdc8e46d58c2</t>
+          <t>https://www.indeed.com/viewjob?jk=8363d4aab2e6b33f</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Architect - Advanced</t>
+          <t>Consultant, Data Analytics</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>Beghou Consulting</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2598e893f85ae2a1</t>
+          <t>https://www.indeed.com/viewjob?jk=53342a3bd9506ed9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Salesforce Developer (Hybrid/Columbia MD)</t>
+          <t>Consultant, Data Analytics</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Beghou Consulting</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfd9cd9ac48b12f</t>
+          <t>https://www.indeed.com/viewjob?jk=1909fc4947c01f17</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Engineering Specialist</t>
+          <t>Consultant, Data Analytics</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Beghou Consulting</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4509b3b48709b4</t>
+          <t>https://www.indeed.com/viewjob?jk=cde8ee2adae9b533</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Platform Engineer, AI Automation</t>
+          <t>Consultant, Data Analytics</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Beghou Consulting</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56f369e5dbe7882</t>
+          <t>https://www.indeed.com/viewjob?jk=1d2caae7d9974108</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Technology, Back End Developer, Senior</t>
+          <t>Consultant, Data Analytics</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Beghou Consulting</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Splunk, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6da938c8f9cc21</t>
+          <t>https://www.indeed.com/viewjob?jk=e47b02d035006ada</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Consultant, Data Analytics</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>El Toro.com</t>
+          <t>Beghou Consulting</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,77 +2341,77 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3113d217a11359b</t>
+          <t>https://www.indeed.com/viewjob?jk=77ed2278b7af9cc7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect - Advanced</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Power BI, DataOps, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583b4c9601400970</t>
+          <t>https://www.indeed.com/viewjob?jk=2598e893f85ae2a1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Foundations)</t>
+          <t>Salesforce Developer (Hybrid/Columbia MD)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6fe26cff174d95</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfd9cd9ac48b12f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SolarWinds</t>
+          <t>Hillpointe</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Winter Park, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Star Schema, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, PostgreSQL, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c073df0d353c1af</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3a3937b7571485</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevSecOps Platform Engineer, AI Automation</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WellBe Senior Medical</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f1be584fe969665</t>
+          <t>https://www.indeed.com/viewjob?jk=d56f369e5dbe7882</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Service Delivery Center, Technology, Back End Developer, Senior</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0289ffc8e0d406cf</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6da938c8f9cc21</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>El Toro.com</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,59 +2561,59 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74ab129070123bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=c3113d217a11359b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Engineering Specialist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add6f4354189f849</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4509b3b48709b4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Architect - Intermediate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Power BI, DataOps, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a36f9ca1924521</t>
+          <t>https://www.indeed.com/viewjob?jk=583b4c9601400970</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior System Engineering - Engineering Operations</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>BambooHR</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cda7123f0312159f</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de96b3860fd283</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Vantive</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99ee79a934f0166</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4303a949ff0206</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Senior Data Engineer (Foundations)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597ef21a1e4293fd</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6fe26cff174d95</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
+          <t>Data and AI Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Data Modeling, Power BI, Tableau, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a92c59262b56cdb</t>
+          <t>https://www.indeed.com/viewjob?jk=efb47d2533a7c899</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SolarWinds</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Star Schema, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,19 +2806,19 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b862d92b1cbb9d</t>
+          <t>https://www.indeed.com/viewjob?jk=1c073df0d353c1af</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Symmetry Lending</t>
+          <t>WellBe Senior Medical</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, CI/CD, Docker</t>
+          <t>AWS, Glue, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1422b190c43693a0</t>
+          <t>https://www.indeed.com/viewjob?jk=9f1be584fe969665</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79da7babfe0a8608</t>
+          <t>https://www.indeed.com/viewjob?jk=0289ffc8e0d406cf</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae21c352f885d87b</t>
+          <t>https://www.indeed.com/viewjob?jk=74ab129070123bd2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ramsey Solutions</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f836a90a9a6c4031</t>
+          <t>https://www.indeed.com/viewjob?jk=add6f4354189f849</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sunikshainfotech</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3b306fbbf582de</t>
+          <t>https://www.indeed.com/viewjob?jk=c99ee79a934f0166</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Vantive</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4303a949ff0206</t>
+          <t>https://www.indeed.com/viewjob?jk=597ef21a1e4293fd</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (AI/Cloud Modernization)</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30265e60609c6fee</t>
+          <t>https://www.indeed.com/viewjob?jk=ae21c352f885d87b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Data Architect - Intermediate</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2682fedab4a2d801</t>
+          <t>https://www.indeed.com/viewjob?jk=53a36f9ca1924521</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior .NET Developer - Full-time (Working from Office)</t>
+          <t>Senior System Engineering - Engineering Operations</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ArsenalTech</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>API Gateway, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=571f6ef27368da0b</t>
+          <t>https://www.indeed.com/viewjob?jk=cda7123f0312159f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Ramsey Solutions</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=971c26dff07c1bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=f836a90a9a6c4031</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>Sunikshainfotech</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,147 +3181,147 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, BigQuery, Vertex AI, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e56c8a333352b48</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3b306fbbf582de</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0733e6d33b962b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=5a92c59262b56cdb</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full Stack Intern</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c15d01008f879b</t>
+          <t>https://www.indeed.com/viewjob?jk=92b862d92b1cbb9d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full Stack Intern</t>
+          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e62e31febbb7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=79da7babfe0a8608</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Senior DevOps Engineer (AI/Cloud Modernization)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Harbinger Motors Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,199 +3331,199 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1042fb894a308b35</t>
+          <t>https://www.indeed.com/viewjob?jk=30265e60609c6fee</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Data Architect</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Octapharma</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4dc84fd3a2c0c7c</t>
+          <t>https://www.indeed.com/viewjob?jk=2682fedab4a2d801</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior .NET Developer - Full-time (Working from Office)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>ArsenalTech</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d57f388e905047</t>
+          <t>https://www.indeed.com/viewjob?jk=571f6ef27368da0b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d13c7e892b0bc19</t>
+          <t>https://www.indeed.com/viewjob?jk=971c26dff07c1bdc</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SDN Automation Engineer</t>
+          <t>Software Engineer II - Identity &amp; Access Management (Core Infra IO)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AIG</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, API Gateway, IAM, RDS, Kafka, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5027122dffca8482</t>
+          <t>https://www.indeed.com/viewjob?jk=d04be766e9c28c71</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Associate - Senior AI Platform Security Engineer</t>
+          <t>Software Engineer II - Identity &amp; Access Management</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, IAM, RDS, Kafka, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60c5181689227fe</t>
+          <t>https://www.indeed.com/viewjob?jk=14aabec8dac5bd65</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Threat Intelligence</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>Rochester Regional Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, PostgreSQL, CI/CD, GitHub Actions, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b6f6e39a72c1b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3a97c6dacfd5cc</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Platform of Greatness</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Git</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a0aff866de84b2</t>
+          <t>https://www.indeed.com/viewjob?jk=0733e6d33b962b4b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Full Stack Intern</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90f91c50a68c29bc</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c15d01008f879b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer – Generative AI</t>
+          <t>Full Stack Intern</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd2d5932a298301</t>
+          <t>https://www.indeed.com/viewjob?jk=15e62e31febbb7dd</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Platform Engineer – Alteryx Platform Owner / Engineer</t>
+          <t>Senior Software Engineer (Data, API &amp; Platform Integration)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,15 +3671,680 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
+          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f645727415a8c94</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b332d7295b6f32a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Sr. Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Harbinger Motors Inc.</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Garden Grove, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1042fb894a308b35</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Integrations</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Worth AI</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ec6348a1a771646</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Integrations</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Worth AI</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=add45f9e195492ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Integrations</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Worth AI</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2053b2017dbd159</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Integrations</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Worth AI</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b7845c99df3c7d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=752a175f328041d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7d0c56dc9911793</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2de604a499b6e351</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Developer II</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5477f4e7c8ef39b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96bd9fb18e41b893</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Sr. Data Architect</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Octapharma</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, NoSQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4dc84fd3a2c0c7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Consultant – Data &amp; Analytics (Microsoft Fabric | Power BI | Databricks)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Quisitive</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, Scala, Dimensional Modeling, Star Schema, ELT</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64e8f6244851402a</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>AT&amp;T</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3d57f388e905047</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Platform of Greatness</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Git</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3a0aff866de84b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d13c7e892b0bc19</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Changeis, Inc.</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Kafka, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90f91c50a68c29bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Full Stack Engineer – Generative AI</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Expleo Group</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Rochester, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bd2d5932a298301</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer – Alteryx Platform Owner / Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MongoDB, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=61d632e85736717d</t>
         </is>
